--- a/src/attributions/attributions_saliency_traj_73.xlsx
+++ b/src/attributions/attributions_saliency_traj_73.xlsx
@@ -2137,2278 +2137,2278 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.004627656191587448</v>
+        <v>6.976410077186301e-05</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01910644024610519</v>
+        <v>3.457432467257604e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002817264059558511</v>
+        <v>7.568749879283132e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002505101729184389</v>
+        <v>1.882653668872081e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003459294384811074</v>
+        <v>1.039978633343708e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01853561215102673</v>
+        <v>0.000111557477794122</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00134726706892252</v>
+        <v>1.121029345085844e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001172271091490984</v>
+        <v>2.921981285908259e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001520483987405896</v>
+        <v>1.848317151598167e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01024447288364172</v>
+        <v>5.492232230608352e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.008850747719407082</v>
+        <v>7.386236393358558e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003875220660120249</v>
+        <v>8.437880751444027e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>0.00325173232704401</v>
+        <v>1.144967427535448e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001615752815268934</v>
+        <v>7.929826097097248e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01354257576167583</v>
+        <v>9.358743409393355e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>0.003348898608237505</v>
+        <v>5.111337304697372e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.003510810667648911</v>
+        <v>2.624063199618831e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002278981963172555</v>
+        <v>4.048445134685608e-06</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0002866339928004891</v>
+        <v>7.595107945235213e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.002116716932505369</v>
+        <v>4.443758734851144e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002879762556403875</v>
+        <v>3.871116859954782e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>0.000444784527644515</v>
+        <v>2.592737018858315e-06</v>
       </c>
       <c r="W4" t="n">
-        <v>0.003449304960668087</v>
+        <v>4.686798274633475e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0001810893299989402</v>
+        <v>5.161085209692828e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.003116728272289038</v>
+        <v>3.295723217888735e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002106426516547799</v>
+        <v>2.381286140007433e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0006903843022882938</v>
+        <v>8.889039236237295e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.004627698566764593</v>
+        <v>1.486480050516548e-05</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.001814966206438839</v>
+        <v>1.209059973916737e-05</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.005046239122748375</v>
+        <v>2.592242708487902e-05</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.001925887539982796</v>
+        <v>1.324787263001781e-06</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.003372818464413285</v>
+        <v>1.123199945141096e-05</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.002337554236873984</v>
+        <v>7.836506483727135e-06</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.003737420774996281</v>
+        <v>8.427409738942515e-06</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.000997263821773231</v>
+        <v>3.730386379174888e-05</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.003668093355372548</v>
+        <v>1.271637484023813e-05</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.0005175495170988142</v>
+        <v>4.982056452718098e-06</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0004730092477984726</v>
+        <v>4.466623522603186e-06</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.002671537455171347</v>
+        <v>5.079318725620396e-06</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.002652636030688882</v>
+        <v>1.666185198700987e-05</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.001375795807689428</v>
+        <v>4.809335223399103e-05</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.003735494799911976</v>
+        <v>2.261059125885367e-05</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.002636542776599526</v>
+        <v>1.911160688905511e-05</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.001069631776772439</v>
+        <v>2.818999746523332e-05</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.003190337680280209</v>
+        <v>1.723383866192307e-05</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.786819484550506e-05</v>
+        <v>7.316597930184798e-06</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.008107900619506836</v>
+        <v>0.0001017926406348124</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.005721305962651968</v>
+        <v>1.081073060049675e-05</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.002750305226072669</v>
+        <v>8.292562370115775e-08</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.00209596729837358</v>
+        <v>1.83904921868816e-06</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.004803005140274763</v>
+        <v>6.820117414463311e-05</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.005629993509501219</v>
+        <v>2.025983576459112e-06</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.288740456104279e-06</v>
+        <v>2.561949440860189e-05</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.00672956183552742</v>
+        <v>8.172698926500743e-07</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.007793613709509373</v>
+        <v>5.984930976410396e-05</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.003951618447899818</v>
+        <v>3.545457730069757e-06</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.004421385936439037</v>
+        <v>1.715148027869873e-05</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.0001273020170629025</v>
+        <v>2.730993946897797e-05</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.0031821692828089</v>
+        <v>2.276788109156769e-05</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.009865329600870609</v>
+        <v>1.660938323766459e-05</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.00441919406875968</v>
+        <v>1.354341293335892e-05</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.001909839222207665</v>
+        <v>4.312951205065474e-05</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.004399507306516171</v>
+        <v>2.242761183879338e-06</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.002453386783599854</v>
+        <v>2.087937355099712e-05</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.003430443350225687</v>
+        <v>3.218862912035547e-05</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.0009154193103313446</v>
+        <v>1.027687903842889e-05</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.001190622104331851</v>
+        <v>6.770701929781353e-06</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.003422156209126115</v>
+        <v>1.724407411529683e-05</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.002087075496092439</v>
+        <v>3.13813507091254e-05</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.001606508856639266</v>
+        <v>2.465008765284438e-05</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.001157996477559209</v>
+        <v>2.09705758607015e-05</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.003081830218434334</v>
+        <v>1.221433763021196e-06</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.0007463960209861398</v>
+        <v>7.919390554889105e-06</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.003870452521368861</v>
+        <v>7.152564194257138e-06</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.004911239258944988</v>
+        <v>2.49125441769138e-05</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.001357319299131632</v>
+        <v>3.24123066093307e-05</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.004554641433060169</v>
+        <v>4.207078018225729e-05</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.0001703058369457722</v>
+        <v>6.418263365048915e-05</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.00111752946395427</v>
+        <v>1.877761133073363e-05</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.0006832801154814661</v>
+        <v>1.0205068065261e-05</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.00175132742151618</v>
+        <v>1.253995924344053e-05</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.000600749917794019</v>
+        <v>3.242917500756448e-06</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.001869928790256381</v>
+        <v>1.418785632267827e-05</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.002710697706788778</v>
+        <v>1.203455121867592e-05</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.0001019420451484621</v>
+        <v>1.101612724596635e-05</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.00134066550526768</v>
+        <v>3.566005943866912e-06</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.003205522894859314</v>
+        <v>2.812141974573024e-05</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.00039782898966223</v>
+        <v>1.18508924060734e-05</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.0004723620950244367</v>
+        <v>7.620014912390616e-06</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.002121710451319814</v>
+        <v>1.071924634743482e-05</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.001969975885003805</v>
+        <v>1.042323765432229e-05</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.005172671284526587</v>
+        <v>5.937921378063038e-05</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.003742493223398924</v>
+        <v>4.152662768319715e-06</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.0005717803724110126</v>
+        <v>7.516253390349448e-06</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.002009231597185135</v>
+        <v>1.988619260373525e-05</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.0005812451709061861</v>
+        <v>2.711515116970986e-05</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.000633527641184628</v>
+        <v>3.167351314914413e-05</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.001364024821668863</v>
+        <v>1.988302756217308e-05</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.00468091806396842</v>
+        <v>1.809336708902265e-06</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0002282063360325992</v>
+        <v>1.821222213038709e-07</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.002007427392527461</v>
+        <v>1.114160113502294e-05</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.002429739572107792</v>
+        <v>5.673278792528436e-06</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.0007069249404594302</v>
+        <v>1.132462784880772e-05</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.001940214773640037</v>
+        <v>7.255412128870375e-06</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.002443345729261637</v>
+        <v>2.387321364949457e-05</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.001050309394486248</v>
+        <v>7.967872988956515e-06</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.0002236849395558238</v>
+        <v>2.774796143967251e-07</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.001935597392730415</v>
+        <v>2.108925173160969e-06</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.001786833396181464</v>
+        <v>2.200448216171935e-05</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.00089870928786695</v>
+        <v>5.465864887810312e-06</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.001893543638288975</v>
+        <v>1.343042458756827e-05</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.003795761382207274</v>
+        <v>8.732036803849041e-06</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.001391915255226195</v>
+        <v>9.679704817244783e-06</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.01050000078976154</v>
+        <v>4.552667087409645e-05</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.003459696657955647</v>
+        <v>9.077178219740745e-06</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.003374349791556597</v>
+        <v>2.996269813593244e-06</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.00693408539518714</v>
+        <v>4.781682946486399e-06</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.003197179641574621</v>
+        <v>1.079020057659363e-05</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.0003093365230597556</v>
+        <v>4.873986654274631e-06</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.002079890808090568</v>
+        <v>2.131213477696292e-05</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0005337392212823033</v>
+        <v>4.496839392231777e-05</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0005321449716575444</v>
+        <v>2.232413316960447e-05</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0008675740682519972</v>
+        <v>2.840514207491651e-05</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.002300908789038658</v>
+        <v>8.284478099085391e-06</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.001597472233697772</v>
+        <v>9.45293595577823e-06</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.003397553460672498</v>
+        <v>3.829930392384995e-06</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.001968293217942119</v>
+        <v>7.949247446958907e-06</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.003340758848935366</v>
+        <v>1.746872658259235e-05</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.001320345443673432</v>
+        <v>4.891056050837506e-06</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.002471378538757563</v>
+        <v>1.231742544405279e-06</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.004037752281874418</v>
+        <v>2.050538387265988e-05</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.0008710026158951223</v>
+        <v>1.819613771658624e-06</v>
       </c>
       <c r="EC4" t="n">
-        <v>4.600506508722901e-05</v>
+        <v>9.61383557296358e-06</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.0007110825972631574</v>
+        <v>2.745558413153049e-05</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.001786591834388673</v>
+        <v>2.318383303645533e-05</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.0006934425910003483</v>
+        <v>1.12405869003851e-05</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.001934989355504513</v>
+        <v>1.38892100949306e-05</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.001049684942699969</v>
+        <v>1.769163827702869e-05</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.002896953839808702</v>
+        <v>5.124033123138361e-06</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.001873726141639054</v>
+        <v>2.230950121884234e-05</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.002059240126982331</v>
+        <v>2.807872806442901e-05</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.00248508807271719</v>
+        <v>5.327912731445394e-06</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0002147784689441323</v>
+        <v>2.838590262399521e-06</v>
       </c>
       <c r="EN4" t="n">
-        <v>1.616653753444552e-05</v>
+        <v>1.128266376326792e-05</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.002556383609771729</v>
+        <v>6.564315299328882e-06</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.0003056387067772448</v>
+        <v>3.254625653426046e-06</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.0009062201716005802</v>
+        <v>2.624403714435175e-05</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.0025965531822294</v>
+        <v>6.137088348623365e-07</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.004253833554685116</v>
+        <v>1.401866938977037e-05</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.004600683692842722</v>
+        <v>3.911635576514527e-05</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.00192448974121362</v>
+        <v>2.151268745365087e-06</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.002515939995646477</v>
+        <v>2.444527126499452e-06</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.00415534246712923</v>
+        <v>2.60115257333382e-06</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.0001738300925353542</v>
+        <v>2.959719040518394e-06</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.002150419866666198</v>
+        <v>1.348634941678029e-05</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.001524890307337046</v>
+        <v>3.35607910528779e-06</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.0003046978381462395</v>
+        <v>1.543214239063673e-05</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.001964869443327188</v>
+        <v>1.354648793494562e-05</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.00170713709667325</v>
+        <v>2.715647133300081e-05</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.001106816343963146</v>
+        <v>1.015390171232866e-05</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.0004421300254762173</v>
+        <v>4.979452114639571e-06</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.002990796463564038</v>
+        <v>4.636583526007598e-06</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.003184412838891149</v>
+        <v>1.44037348945858e-05</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.0004974580369889736</v>
+        <v>6.697719072690234e-06</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.001215242664329708</v>
+        <v>1.636609795241384e-06</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.003513095667585731</v>
+        <v>9.065233825822361e-06</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.003445832524448633</v>
+        <v>3.424095848458819e-05</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.004205111414194107</v>
+        <v>1.278892341360915e-06</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.0004019547486677766</v>
+        <v>7.590477252961136e-06</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.0002299815823789686</v>
+        <v>1.770162089087535e-05</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.004441379103809595</v>
+        <v>1.474737746320898e-05</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.002139029558748007</v>
+        <v>3.557898889994249e-05</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.003400169080123305</v>
+        <v>4.167047791270306e-07</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.003263950115069747</v>
+        <v>1.885142228275072e-05</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.001747032627463341</v>
+        <v>7.777845894452184e-06</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0005160427535884082</v>
+        <v>4.339281440479681e-05</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.006311664823442698</v>
+        <v>5.203345608606469e-06</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.001933231251314282</v>
+        <v>5.719801993109286e-05</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.0001473765005357563</v>
+        <v>2.812089587678201e-05</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.00416602985933423</v>
+        <v>2.956843218271388e-06</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.004654557444155216</v>
+        <v>2.781342482194304e-05</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.001828845008276403</v>
+        <v>1.781661558197811e-05</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.001469543436542153</v>
+        <v>5.816036264150171e-06</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.002649522153660655</v>
+        <v>7.27763199392939e-06</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.003153214463964105</v>
+        <v>3.850402572425082e-05</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.0007257170509546995</v>
+        <v>3.296727663837373e-05</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.0001531197922304273</v>
+        <v>1.452646392863244e-05</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.001771219773218036</v>
+        <v>2.851005774573423e-06</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.004899945575743914</v>
+        <v>1.270738721359521e-05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0805729553103447</v>
+        <v>0.04474472627043724</v>
       </c>
       <c r="B5" t="n">
-        <v>0.659181535243988</v>
+        <v>1.349049091339111</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04558011144399643</v>
+        <v>0.1630859822034836</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3334438800811768</v>
+        <v>1.242480158805847</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1648459434509277</v>
+        <v>0.2831682860851288</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1006290838122368</v>
+        <v>0.4017162621021271</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03947011381387711</v>
+        <v>0.4024712741374969</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08038155734539032</v>
+        <v>0.4326099455356598</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05896021053195</v>
+        <v>0.1899457573890686</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1184384673833847</v>
+        <v>0.06981989741325378</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4884740710258484</v>
+        <v>1.301186919212341</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009771688841283321</v>
+        <v>0.2972851097583771</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3152313530445099</v>
+        <v>1.598830461502075</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1999519169330597</v>
+        <v>0.6046569347381592</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1619072705507278</v>
+        <v>0.333125114440918</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0333046168088913</v>
+        <v>0.3088382184505463</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06157969683408737</v>
+        <v>0.0873168557882309</v>
       </c>
       <c r="R5" t="n">
-        <v>0.08085929602384567</v>
+        <v>0.04387462139129639</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01411380711942911</v>
+        <v>0.0437016636133194</v>
       </c>
       <c r="T5" t="n">
-        <v>0.04257465153932571</v>
+        <v>0.00760720856487751</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03100708499550819</v>
+        <v>0.01215858571231365</v>
       </c>
       <c r="V5" t="n">
-        <v>0.09541222453117371</v>
+        <v>0.007666334509849548</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2527326643466949</v>
+        <v>0.03318245708942413</v>
       </c>
       <c r="X5" t="n">
-        <v>0.007173523306846619</v>
+        <v>0.2032312750816345</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0732303261756897</v>
+        <v>0.1768529415130615</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.08675581961870193</v>
+        <v>0.2604978978633881</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.06496128439903259</v>
+        <v>0.1119992583990097</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02197801321744919</v>
+        <v>0.05448650196194649</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1077118143439293</v>
+        <v>0.09550980478525162</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.005247936118394136</v>
+        <v>0.1622059941291809</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0164849329739809</v>
+        <v>0.1545054763555527</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.117678128182888</v>
+        <v>0.2118758708238602</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.08868909627199173</v>
+        <v>0.5122789144515991</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.002916596829891205</v>
+        <v>0.05444679036736488</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.03547284379601479</v>
+        <v>0.2373881042003632</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.03484655171632767</v>
+        <v>0.0785171240568161</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.02768936939537525</v>
+        <v>0.06122078746557236</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.1120888739824295</v>
+        <v>0.4012542963027954</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.00295187858864665</v>
+        <v>0.1892612278461456</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.02526114508509636</v>
+        <v>0.2501857280731201</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.08915361762046814</v>
+        <v>0.2560349106788635</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.108704537153244</v>
+        <v>0.2237525880336761</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.01919538527727127</v>
+        <v>0.152526319026947</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.0006470624357461929</v>
+        <v>0.01677647233009338</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.06377816200256348</v>
+        <v>0.06649214029312134</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.00804281048476696</v>
+        <v>0.05283910408616066</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.289821594953537</v>
+        <v>0.6192672252655029</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.02030909806489944</v>
+        <v>0.1619783639907837</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.1189046949148178</v>
+        <v>0.4041646718978882</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.149134561419487</v>
+        <v>0.6991984248161316</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.1920257955789566</v>
+        <v>0.3588930070400238</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.06914012879133224</v>
+        <v>0.000407882034778595</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.1080848053097725</v>
+        <v>0.08750145882368088</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.02218728512525558</v>
+        <v>0.1486583650112152</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.07002273201942444</v>
+        <v>0.1063041463494301</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.1666788756847382</v>
+        <v>0.1961226314306259</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.04838596656918526</v>
+        <v>0.218266025185585</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.07804300636053085</v>
+        <v>0.161660835146904</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.1068220809102058</v>
+        <v>0.1784175038337708</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.01116070710122585</v>
+        <v>0.158219575881958</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.06921906769275665</v>
+        <v>0.1200146973133087</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.05911730974912643</v>
+        <v>0.3863934278488159</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.06534262001514435</v>
+        <v>0.08771418035030365</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.03037770837545395</v>
+        <v>0.008685668930411339</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.04683844000101089</v>
+        <v>0.2007649838924408</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.02890747785568237</v>
+        <v>0.04301909357309341</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.01723472587764263</v>
+        <v>0.3844096064567566</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.03622737899422646</v>
+        <v>0.1046083718538284</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.03464311361312866</v>
+        <v>0.008338066749274731</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.001733556389808655</v>
+        <v>0.1774954944849014</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.08696934580802917</v>
+        <v>0.1441636085510254</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.009196564555168152</v>
+        <v>0.1152835115790367</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.0215056911110878</v>
+        <v>0.04454921185970306</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1972991675138474</v>
+        <v>0.50041663646698</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.03924573212862015</v>
+        <v>0.09828856587409973</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.1565408259630203</v>
+        <v>0.5416487455368042</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.1353989094495773</v>
+        <v>0.00809834897518158</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.009489349089562893</v>
+        <v>0.1698008328676224</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.02901636250317097</v>
+        <v>0.1228734403848648</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.08564026653766632</v>
+        <v>0.01814574562013149</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.06414660811424255</v>
+        <v>0.006347563117742538</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.005686037708073854</v>
+        <v>0.01195160299539566</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.1046133488416672</v>
+        <v>0.4477343559265137</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.0310297142714262</v>
+        <v>0.01783407852053642</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.05433324351906776</v>
+        <v>0.4485664963722229</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.01810221374034882</v>
+        <v>0.0003647103440016508</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.01914845407009125</v>
+        <v>0.06062594428658485</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0163902509957552</v>
+        <v>0.09672009199857712</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.01225815247744322</v>
+        <v>0.07559653371572495</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.02491309866309166</v>
+        <v>0.03397459164261818</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.03121533431112766</v>
+        <v>0.1388845592737198</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.06165950000286102</v>
+        <v>0.3678721785545349</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.04720769077539444</v>
+        <v>0.4111765325069427</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.04316963255405426</v>
+        <v>0.5836747884750366</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.06860322505235672</v>
+        <v>0.0005123130977153778</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.04801267385482788</v>
+        <v>0.1197021901607513</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.1053146570920944</v>
+        <v>0.288237988948822</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.1292703449726105</v>
+        <v>0.2136642038822174</v>
       </c>
       <c r="CU5" t="n">
-        <v>3.688037395477295e-06</v>
+        <v>0.03777128830552101</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.003802748396992683</v>
+        <v>0.005770397372543812</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.09913945943117142</v>
+        <v>0.4347845017910004</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.03428865596652031</v>
+        <v>0.0581524521112442</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.06239782646298409</v>
+        <v>0.4680051207542419</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.02071691676974297</v>
+        <v>0.09923112392425537</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.02267096191644669</v>
+        <v>0.06586808711290359</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0116991363465786</v>
+        <v>0.105367586016655</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.01759782247245312</v>
+        <v>0.1016148179769516</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.02092881128191948</v>
+        <v>0.001241152174770832</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.05464077368378639</v>
+        <v>0.1453292220830917</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.1692178249359131</v>
+        <v>0.2766427397727966</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.04896014928817749</v>
+        <v>0.03497262671589851</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.2528499662876129</v>
+        <v>0.4430601894855499</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.1469275206327438</v>
+        <v>0.1386446356773376</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.04312300309538841</v>
+        <v>0.4403888583183289</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.07398434728384018</v>
+        <v>0.1742902249097824</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.09187912940979004</v>
+        <v>0.7825642228126526</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.04543942958116531</v>
+        <v>0.03941658139228821</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.05819239467382431</v>
+        <v>0.04570389539003372</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.07940483093261719</v>
+        <v>0.2379906922578812</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.000211627222597599</v>
+        <v>0.0135798454284668</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.06543721258640289</v>
+        <v>0.3469275832176208</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.01657052338123322</v>
+        <v>0.0003725346177816391</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.0583343543112278</v>
+        <v>0.07845747470855713</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.01324095204472542</v>
+        <v>0.28444704413414</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.006195006892085075</v>
+        <v>0.1768438220024109</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.07576997578144073</v>
+        <v>0.5879162549972534</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.01596148312091827</v>
+        <v>0.01786151528358459</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.001257362077012658</v>
+        <v>0.09834395349025726</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.03584510460495949</v>
+        <v>0.1965270340442657</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0295376218855381</v>
+        <v>0.08030018210411072</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.06034328788518906</v>
+        <v>0.03709473460912704</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.001711275428533554</v>
+        <v>0.1656980663537979</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.01077819149941206</v>
+        <v>0.1744800508022308</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.03712613880634308</v>
+        <v>0.7796091437339783</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.008616527542471886</v>
+        <v>0.4192808270454407</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.04859204590320587</v>
+        <v>0.1479890942573547</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.04034176096320152</v>
+        <v>0.2940966784954071</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.03911776840686798</v>
+        <v>0.1952951848506927</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.008640190586447716</v>
+        <v>0.4591864049434662</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.03408132493495941</v>
+        <v>0.2428368479013443</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.003495640587061644</v>
+        <v>0.03372405469417572</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.01138676609843969</v>
+        <v>0.08623304963111877</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.001204212778247893</v>
+        <v>0.0002353342715650797</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.0206505861133337</v>
+        <v>0.05043408274650574</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.0370585098862648</v>
+        <v>0.1239421740174294</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.05939488112926483</v>
+        <v>0.4314453303813934</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.02558723092079163</v>
+        <v>0.03346718847751617</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.08351318538188934</v>
+        <v>0.1860443949699402</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.000701315701007843</v>
+        <v>0.02805792354047298</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.1248432695865631</v>
+        <v>0.09037285298109055</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.06498431414365768</v>
+        <v>0.1764332354068756</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.08651462197303772</v>
+        <v>0.2195801287889481</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.009017836302518845</v>
+        <v>0.2308809459209442</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.0010335105471313</v>
+        <v>0.02754739671945572</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.08805640786886215</v>
+        <v>0.4643524885177612</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.02286211773753166</v>
+        <v>0.02675808593630791</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.06438346952199936</v>
+        <v>0.548163890838623</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.006061957683414221</v>
+        <v>0.02659904584288597</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.02811979129910469</v>
+        <v>0.06059572473168373</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.03822628408670425</v>
+        <v>0.06493385881185532</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.02543891035020351</v>
+        <v>0.1247179359197617</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.0397457629442215</v>
+        <v>0.04056567698717117</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.01110910903662443</v>
+        <v>0.01954946294426918</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.05440298095345497</v>
+        <v>0.1330147385597229</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.006360474042594433</v>
+        <v>0.07380837202072144</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.02349107712507248</v>
+        <v>0.3539789617061615</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.07076065242290497</v>
+        <v>0.02417139708995819</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.0002510193735361099</v>
+        <v>0.004915472120046616</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.01303909253329039</v>
+        <v>0.02406393736600876</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.025649044662714</v>
+        <v>0.2975365817546844</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.0019539431668818</v>
+        <v>0.02372405305504799</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.08060500025749207</v>
+        <v>0.2214892208576202</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.04180864989757538</v>
+        <v>0.4835830330848694</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.05478345975279808</v>
+        <v>0.1778941750526428</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.01681971922516823</v>
+        <v>0.04679671674966812</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.011226586997509</v>
+        <v>0.1685290783643723</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.008029060438275337</v>
+        <v>0.2807837724685669</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0239902064204216</v>
+        <v>0.07782691717147827</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.01738754287362099</v>
+        <v>0.05556128174066544</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.02111054770648479</v>
+        <v>0.448318749666214</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.01259524188935757</v>
+        <v>0.138853058218956</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.02465988323092461</v>
+        <v>0.1694910079240799</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.005865065380930901</v>
+        <v>0.05834778398275375</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.006733778864145279</v>
+        <v>0.3068189024925232</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.2482014149427414</v>
+        <v>0.2222055643796921</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.09821218252182007</v>
+        <v>0.1003567203879356</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.1885558366775513</v>
+        <v>0.2376340627670288</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.03765353187918663</v>
+        <v>0.1484539210796356</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.02192019671201706</v>
+        <v>0.01155447587370872</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.002945275977253914</v>
+        <v>4.656101025568571e-12</v>
       </c>
       <c r="B6" t="n">
-        <v>0.002949543297290802</v>
+        <v>5.519472465881359e-12</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002083004219457507</v>
+        <v>7.819384029161824e-12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0003300284733995795</v>
+        <v>3.797499207452981e-12</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004230265505611897</v>
+        <v>8.43663854055432e-12</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002434411086142063</v>
+        <v>2.770684549846525e-11</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001641447190195322</v>
+        <v>1.371885070822199e-11</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001124982722103596</v>
+        <v>1.221046961458194e-11</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00443218182772398</v>
+        <v>1.53729839188349e-13</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001601861556991935</v>
+        <v>4.549342673410006e-13</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004866354167461395</v>
+        <v>2.585136965604917e-13</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003778717014938593</v>
+        <v>9.915603060850486e-12</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001123447902500629</v>
+        <v>1.060798931334928e-11</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001360248192213476</v>
+        <v>1.146356447268015e-11</v>
       </c>
       <c r="O6" t="n">
-        <v>3.990111872553825e-05</v>
+        <v>3.422988975598784e-11</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001877806149423122</v>
+        <v>2.044156857672341e-11</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.003606863087043166</v>
+        <v>1.077623060230515e-11</v>
       </c>
       <c r="R6" t="n">
-        <v>4.810903192264959e-05</v>
+        <v>5.495104805214313e-12</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001174131408333778</v>
+        <v>2.762904705369551e-12</v>
       </c>
       <c r="T6" t="n">
-        <v>0.004073468968272209</v>
+        <v>4.950350893095923e-12</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001240941463038325</v>
+        <v>1.7408771906674e-12</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001478548045270145</v>
+        <v>3.502283966311248e-12</v>
       </c>
       <c r="W6" t="n">
-        <v>0.004999409429728985</v>
+        <v>1.502335929270959e-11</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001914562308229506</v>
+        <v>3.359211780268323e-12</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0003845763276331127</v>
+        <v>3.351173505361515e-13</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002132144756615162</v>
+        <v>4.471866887206799e-12</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0004192774067632854</v>
+        <v>1.405096742082557e-12</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0009317923104390502</v>
+        <v>3.728103329520005e-12</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.001506555010564625</v>
+        <v>2.334129851205846e-12</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.003817287040874362</v>
+        <v>1.730266104005285e-12</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.0009574359282851219</v>
+        <v>7.781045772980999e-12</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.003726127557456493</v>
+        <v>1.464697807485038e-11</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.001874544890597463</v>
+        <v>8.818691436818238e-12</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.005199641920626163</v>
+        <v>8.910589280319847e-12</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.000897360616363585</v>
+        <v>8.808235391066788e-12</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.004641830455511808</v>
+        <v>5.287408531839954e-12</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.001545245992019773</v>
+        <v>1.221146664689976e-12</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.002168426755815744</v>
+        <v>5.360954735689205e-13</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.0004127501451876014</v>
+        <v>5.028798558126546e-13</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.003254337701946497</v>
+        <v>5.24010132160746e-12</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.002800742862746119</v>
+        <v>1.377385532019826e-11</v>
       </c>
       <c r="AP6" t="n">
-        <v>9.913793473970145e-05</v>
+        <v>2.788526354269294e-12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.001743071596138179</v>
+        <v>2.916435322408706e-12</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.572555189952254e-05</v>
+        <v>1.025680842342558e-12</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.0005045584985055029</v>
+        <v>5.185792333745054e-12</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.004425897262990475</v>
+        <v>3.33606319652402e-12</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.003799829166382551</v>
+        <v>7.45802204715762e-12</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.001494734897278249</v>
+        <v>5.148822774386774e-12</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.005577274598181248</v>
+        <v>1.223715573317463e-12</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.00968653429299593</v>
+        <v>4.673797807108748e-12</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.001105265342630446</v>
+        <v>1.990999032308594e-11</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.008316474966704845</v>
+        <v>8.440126202102771e-12</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.007200839929282665</v>
+        <v>1.302116140605714e-11</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.002968721091747284</v>
+        <v>5.343538111990398e-13</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.004079138860106468</v>
+        <v>7.354746152377079e-12</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.001464621280319989</v>
+        <v>2.42411125894737e-12</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.001017802394926548</v>
+        <v>5.407923241163015e-12</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.0008071223273873329</v>
+        <v>1.324653407797083e-11</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.002150138141587377</v>
+        <v>1.449895759009223e-12</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.0004605072026606649</v>
+        <v>5.998339845658673e-12</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.004661235958337784</v>
+        <v>1.62260656300095e-12</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.003043482778593898</v>
+        <v>1.138229918304368e-12</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.00107003131415695</v>
+        <v>4.078729541612258e-12</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.0007645469158887863</v>
+        <v>1.967993910195753e-12</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.0007741264416836202</v>
+        <v>3.392002824453844e-12</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.001333922031335533</v>
+        <v>4.572971775557155e-12</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.007478198036551476</v>
+        <v>3.342178693088033e-13</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.004853948950767517</v>
+        <v>3.021869213193362e-12</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.0009624478407204151</v>
+        <v>3.178282506968721e-12</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.001555659691803157</v>
+        <v>3.253930761989987e-12</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.003978058230131865</v>
+        <v>1.157336162668776e-12</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.003636373672634363</v>
+        <v>7.978848484690992e-12</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.002118152100592852</v>
+        <v>8.620195486239157e-13</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.001884733093902469</v>
+        <v>7.023815556950197e-12</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.001795295043848455</v>
+        <v>2.994528019648057e-12</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.001403578324243426</v>
+        <v>1.358091156894448e-11</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.00449790945276618</v>
+        <v>2.081660538388874e-11</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.002132849069312215</v>
+        <v>1.112192022506564e-11</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.003306663129478693</v>
+        <v>6.28068300492779e-12</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.003422090550884604</v>
+        <v>1.849590793023825e-12</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.0007196698570623994</v>
+        <v>7.067760439405379e-12</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.489994560368359e-05</v>
+        <v>2.839356354200628e-13</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.001287379884161055</v>
+        <v>8.283400007580433e-13</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.0002312841825187206</v>
+        <v>2.505403003116857e-12</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.001850035507231951</v>
+        <v>1.683164024823824e-12</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.0007959292852319777</v>
+        <v>2.614501930925384e-12</v>
       </c>
       <c r="CI6" t="n">
-        <v>5.518072794075124e-05</v>
+        <v>7.708588975474662e-12</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.000174964196048677</v>
+        <v>3.103646679936123e-12</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.0004098150529898703</v>
+        <v>3.385213550449739e-12</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.367363438475877e-05</v>
+        <v>3.968798380216132e-12</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.002196361776441336</v>
+        <v>1.183033705720593e-13</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.005254742223769426</v>
+        <v>4.779318867748072e-12</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.0006863601738587022</v>
+        <v>1.812247075495821e-12</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.0004872472491115332</v>
+        <v>9.887147524312301e-13</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.00535264378413558</v>
+        <v>1.140239118402331e-11</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.002544790739193559</v>
+        <v>3.999665182385925e-12</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.001606602338142693</v>
+        <v>5.062398417132741e-12</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.001232974696904421</v>
+        <v>5.210638344410601e-12</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.003788211150094867</v>
+        <v>4.826847255223754e-12</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.685579238459468e-05</v>
+        <v>4.262703471452634e-14</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.0012672352604568</v>
+        <v>1.289242801058577e-12</v>
       </c>
       <c r="CX6" t="n">
-        <v>5.919046816416085e-05</v>
+        <v>1.986565642889127e-12</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.002037311671301723</v>
+        <v>2.809622976981951e-12</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.0004800477472599596</v>
+        <v>2.260765793321573e-12</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.001159589854069054</v>
+        <v>8.702863082965528e-12</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.0008319439366459846</v>
+        <v>2.813343958837922e-12</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.0004851632402278483</v>
+        <v>3.623428380256088e-12</v>
       </c>
       <c r="DD6" t="n">
-        <v>8.82989406818524e-05</v>
+        <v>3.424742477456388e-12</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.004325348418205976</v>
+        <v>4.836350070425155e-12</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.006779760587960482</v>
+        <v>1.97684750513627e-11</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.0001557875366415828</v>
+        <v>7.501516768870786e-12</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.002992480061948299</v>
+        <v>1.908720577425971e-13</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.002334775170311332</v>
+        <v>3.048039251551948e-12</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.008874017745256424</v>
+        <v>1.945899691380149e-11</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.0008430045563727617</v>
+        <v>8.839252246817253e-12</v>
       </c>
       <c r="DL6" t="n">
-        <v>7.03333062119782e-05</v>
+        <v>2.040142143763801e-12</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.006197513081133366</v>
+        <v>9.179419377391973e-12</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.0006077780853956938</v>
+        <v>2.766328398989826e-12</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.002396468073129654</v>
+        <v>3.617077340770103e-12</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.0001867223036242649</v>
+        <v>6.044928880372114e-12</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.0005703491624444723</v>
+        <v>1.473965220710749e-11</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.002198113361373544</v>
+        <v>3.660991215043152e-12</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.001651499187573791</v>
+        <v>2.88450470106727e-13</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.002459676470607519</v>
+        <v>3.205335953257449e-12</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.0006977462326176465</v>
+        <v>5.999815227974992e-12</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.004841084126383066</v>
+        <v>3.760605108565906e-12</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.0003786675806622952</v>
+        <v>3.576309387520737e-12</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.0006391622591763735</v>
+        <v>3.757395002773611e-12</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.0004908134578727186</v>
+        <v>2.078481917827668e-12</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.004876085557043552</v>
+        <v>6.293271893192953e-12</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.002412516390904784</v>
+        <v>1.423670209499406e-13</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.001053875777870417</v>
+        <v>4.472018241830078e-12</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.0001723184832371771</v>
+        <v>3.416455703411647e-12</v>
       </c>
       <c r="ED6" t="n">
-        <v>7.949670543894172e-05</v>
+        <v>7.292560652572e-13</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.002282365458086133</v>
+        <v>7.782022422297974e-12</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.001104319817386568</v>
+        <v>3.533866341914882e-12</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.001462725573219359</v>
+        <v>4.612569007300671e-13</v>
       </c>
       <c r="EH6" t="n">
-        <v>2.89541876554722e-05</v>
+        <v>7.336967405152661e-13</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.004866211675107479</v>
+        <v>1.036430229833796e-11</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.001283848192542791</v>
+        <v>5.614772535800228e-12</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.003635663772001863</v>
+        <v>3.814072755542464e-12</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.001014045090414584</v>
+        <v>1.239348901282966e-12</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.001879013609141111</v>
+        <v>4.844655059066394e-12</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.0002684787032194436</v>
+        <v>1.012632946245651e-11</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.0002276477171108127</v>
+        <v>1.055906989448629e-12</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.0004501552321016788</v>
+        <v>2.267949500076027e-12</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.0005218226579017937</v>
+        <v>1.687822407878126e-12</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.0003122655616607517</v>
+        <v>1.36976237644082e-12</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.0003328346647322178</v>
+        <v>1.330447384206845e-11</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.001359533052891493</v>
+        <v>7.397727395941356e-12</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.002723997691646218</v>
+        <v>4.291567535369412e-12</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.002422470133751631</v>
+        <v>1.529269332695149e-13</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.002370955422520638</v>
+        <v>2.324643299037032e-13</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.0003487562062218785</v>
+        <v>2.286108585422553e-13</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.001188914407975972</v>
+        <v>1.685754617494761e-12</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.0004530357546173036</v>
+        <v>1.993660661905872e-12</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.001945370342582464</v>
+        <v>1.761545878782578e-12</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.0006807182799093425</v>
+        <v>3.481980329067547e-14</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.0007895956514403224</v>
+        <v>7.147276694097204e-12</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.0004201397532597184</v>
+        <v>2.580732069018543e-12</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.001340264570899308</v>
+        <v>3.846999975520848e-12</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.0006713453331030905</v>
+        <v>1.958844111221714e-12</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.002312124008312821</v>
+        <v>3.293207069890447e-12</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.001759249484166503</v>
+        <v>3.43501052255113e-12</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.0007730742800049484</v>
+        <v>7.07112320086356e-12</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.003369340440258384</v>
+        <v>7.64636617911485e-12</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.000235977116972208</v>
+        <v>8.950038626887036e-12</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.002340168692171574</v>
+        <v>2.249145531277308e-12</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.0006661857478320599</v>
+        <v>3.452765417327752e-12</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.0005705761141143739</v>
+        <v>8.202162907200439e-12</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.001948504708707333</v>
+        <v>4.901721389893865e-12</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.001599454204551876</v>
+        <v>9.432185935076554e-12</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.001591545296832919</v>
+        <v>1.262287756959024e-11</v>
       </c>
       <c r="FR6" t="n">
-        <v>7.002625352470204e-05</v>
+        <v>1.383902627910549e-11</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.002191148232668638</v>
+        <v>8.536628001709623e-12</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.01307939924299717</v>
+        <v>1.19194688841251e-11</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.005517425015568733</v>
+        <v>1.070909593642311e-11</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.004878893494606018</v>
+        <v>1.354574438727774e-11</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.002470466773957014</v>
+        <v>4.513531041971941e-12</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.002540749264881015</v>
+        <v>3.423246495298793e-12</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.001414901809766889</v>
+        <v>2.700724843415769e-12</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.002917855512350798</v>
+        <v>2.387914518897638e-12</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.002092995215207338</v>
+        <v>2.317452870229109e-12</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.004896092694252729</v>
+        <v>8.292810015075869e-12</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.003528980072587729</v>
+        <v>4.940875399789268e-12</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.003121333662420511</v>
+        <v>1.079627359734658e-11</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.004646610002964735</v>
+        <v>1.005768927343775e-12</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.006972754839807749</v>
+        <v>8.767424286570957e-12</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.006905810441821814</v>
+        <v>3.729737872715244e-12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>8.915125363273546e-06</v>
+        <v>1.860375731504299e-14</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0002925009466707706</v>
+        <v>3.809223376722952e-14</v>
       </c>
       <c r="C7" t="n">
-        <v>9.435605898033828e-05</v>
+        <v>6.915233901998163e-14</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0002178308495786041</v>
+        <v>4.7497338635967e-14</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0004229014448355883</v>
+        <v>3.335922372214341e-14</v>
       </c>
       <c r="F7" t="n">
-        <v>9.747884178068489e-05</v>
+        <v>1.296425260980533e-13</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001961565285455436</v>
+        <v>1.811518024073724e-14</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001267923507839441</v>
+        <v>4.086745929187709e-15</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0003558027383405715</v>
+        <v>9.585098014776305e-14</v>
       </c>
       <c r="J7" t="n">
-        <v>8.720227924641222e-05</v>
+        <v>1.906845991869743e-14</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001233329094247892</v>
+        <v>1.459774683944259e-13</v>
       </c>
       <c r="L7" t="n">
-        <v>4.420976620167494e-05</v>
+        <v>6.651328251193467e-14</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0003014054673258215</v>
+        <v>1.151730891647135e-13</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0004967742133885622</v>
+        <v>6.014062674513515e-15</v>
       </c>
       <c r="O7" t="n">
-        <v>6.410582500393502e-06</v>
+        <v>9.591989474835166e-14</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0001327888749074191</v>
+        <v>3.627794679245122e-14</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.539797247271053e-06</v>
+        <v>3.062828446811008e-14</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0002404109982308</v>
+        <v>5.60175210796536e-14</v>
       </c>
       <c r="S7" t="n">
-        <v>1.264152797375573e-05</v>
+        <v>2.548616767389551e-14</v>
       </c>
       <c r="T7" t="n">
-        <v>8.979692938737571e-05</v>
+        <v>6.480209977562795e-14</v>
       </c>
       <c r="U7" t="n">
-        <v>7.075882604112849e-05</v>
+        <v>2.067348062759298e-14</v>
       </c>
       <c r="V7" t="n">
-        <v>2.376178599661216e-05</v>
+        <v>4.97096768858462e-14</v>
       </c>
       <c r="W7" t="n">
-        <v>0.000109047228761483</v>
+        <v>1.124506846146567e-13</v>
       </c>
       <c r="X7" t="n">
-        <v>3.716840001288801e-05</v>
+        <v>5.900823856234624e-14</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.833485480863601e-06</v>
+        <v>2.483201429312638e-14</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.364050305914134e-05</v>
+        <v>2.477565610894787e-14</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.453746052808128e-05</v>
+        <v>2.38934136961421e-14</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.680137059651315e-07</v>
+        <v>2.435451471570482e-14</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0001209292895509861</v>
+        <v>1.441102215316535e-14</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0001596192305441946</v>
+        <v>4.207597540783342e-14</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.0001242627768078819</v>
+        <v>6.198554581941795e-14</v>
       </c>
       <c r="AF7" t="n">
-        <v>3.716546416399069e-05</v>
+        <v>2.372952637337555e-15</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0001177863014163449</v>
+        <v>4.393324761061898e-14</v>
       </c>
       <c r="AH7" t="n">
-        <v>6.796322122681886e-05</v>
+        <v>1.747139962544018e-14</v>
       </c>
       <c r="AI7" t="n">
-        <v>8.59077917994e-05</v>
+        <v>5.974783385057081e-14</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0001184923385153525</v>
+        <v>1.248624057745068e-14</v>
       </c>
       <c r="AK7" t="n">
-        <v>4.525299664237536e-05</v>
+        <v>4.166329756779934e-14</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.000128526400658302</v>
+        <v>2.796666469641416e-14</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.447720933356322e-05</v>
+        <v>1.748656320926193e-14</v>
       </c>
       <c r="AN7" t="n">
-        <v>4.927339978166856e-05</v>
+        <v>6.874164323704413e-14</v>
       </c>
       <c r="AO7" t="n">
-        <v>3.591714994399808e-05</v>
+        <v>4.903686506331495e-14</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.0001207369568874128</v>
+        <v>1.374009836707353e-15</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.731066160777118e-05</v>
+        <v>8.910486755451912e-15</v>
       </c>
       <c r="AR7" t="n">
-        <v>7.346560323640006e-06</v>
+        <v>3.269786378505904e-14</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.216749635408632e-05</v>
+        <v>2.435372866912977e-14</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.468253973755054e-05</v>
+        <v>1.14704532561149e-14</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.0004181551048532128</v>
+        <v>1.519620746511657e-13</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.958913268637843e-05</v>
+        <v>9.593223263026137e-15</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.666914951987565e-05</v>
+        <v>1.984191789008733e-14</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.322538628301118e-05</v>
+        <v>3.720355051589283e-14</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.0001901212090160698</v>
+        <v>6.283764741182862e-15</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.0001287127670366317</v>
+        <v>4.22235336294428e-15</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.0001411712728440762</v>
+        <v>4.039976835598473e-14</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.458379306830466e-05</v>
+        <v>2.186900834033612e-14</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.012803740100935e-05</v>
+        <v>3.503222898945148e-14</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.0001728806819301099</v>
+        <v>2.257682464644559e-14</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.799647235311568e-05</v>
+        <v>2.069470896731707e-16</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.0002700408222153783</v>
+        <v>4.414484660523847e-14</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.0001684429444139823</v>
+        <v>2.676201782696088e-14</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.181671218044357e-06</v>
+        <v>6.780680346634566e-14</v>
       </c>
       <c r="BI7" t="n">
-        <v>9.683161624707282e-05</v>
+        <v>4.421087112941105e-14</v>
       </c>
       <c r="BJ7" t="n">
-        <v>2.310462150489911e-05</v>
+        <v>4.593581645704475e-14</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.0003990272816736251</v>
+        <v>3.493049694435445e-14</v>
       </c>
       <c r="BL7" t="n">
-        <v>9.328767191618681e-05</v>
+        <v>3.671401290622489e-14</v>
       </c>
       <c r="BM7" t="n">
-        <v>7.017144525889307e-06</v>
+        <v>4.679034733994815e-14</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.0001035401437547989</v>
+        <v>4.314394080575301e-16</v>
       </c>
       <c r="BO7" t="n">
-        <v>7.741240551695228e-05</v>
+        <v>1.208627839602077e-14</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0002293998986715451</v>
+        <v>7.127419043417155e-14</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.489306931849569e-05</v>
+        <v>5.330647015922181e-14</v>
       </c>
       <c r="BR7" t="n">
-        <v>6.981020123930648e-05</v>
+        <v>5.836583522262143e-14</v>
       </c>
       <c r="BS7" t="n">
-        <v>8.869825978763402e-05</v>
+        <v>2.16609651900292e-14</v>
       </c>
       <c r="BT7" t="n">
-        <v>3.770101102418266e-05</v>
+        <v>1.781406849831781e-14</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.702152753248811e-05</v>
+        <v>1.550850410819791e-15</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.000292379321763292</v>
+        <v>2.531340852803942e-14</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.0001663491129875183</v>
+        <v>3.785524072485134e-14</v>
       </c>
       <c r="BX7" t="n">
-        <v>7.597403964609839e-06</v>
+        <v>6.041085058410001e-14</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.802350203040987e-05</v>
+        <v>6.549606370491803e-14</v>
       </c>
       <c r="BZ7" t="n">
-        <v>4.904329762212001e-05</v>
+        <v>7.150416326748288e-14</v>
       </c>
       <c r="CA7" t="n">
-        <v>5.080809205537662e-05</v>
+        <v>8.670754408522316e-15</v>
       </c>
       <c r="CB7" t="n">
-        <v>7.689833728363737e-05</v>
+        <v>5.126505976996674e-14</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0001067608463927172</v>
+        <v>5.175534276862827e-14</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.215039891481865e-06</v>
+        <v>7.632495303095885e-15</v>
       </c>
       <c r="CE7" t="n">
-        <v>4.940866347169504e-05</v>
+        <v>8.229008938837306e-15</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.693359783734195e-05</v>
+        <v>1.116808028163701e-14</v>
       </c>
       <c r="CG7" t="n">
-        <v>4.894983794656582e-05</v>
+        <v>2.320374930609229e-14</v>
       </c>
       <c r="CH7" t="n">
-        <v>8.12083380878903e-05</v>
+        <v>6.552922165667125e-15</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.309371848241426e-05</v>
+        <v>2.746825865178847e-14</v>
       </c>
       <c r="CJ7" t="n">
-        <v>8.915126272768248e-06</v>
+        <v>7.575984652986867e-15</v>
       </c>
       <c r="CK7" t="n">
-        <v>3.61545680789277e-05</v>
+        <v>5.316551794756806e-15</v>
       </c>
       <c r="CL7" t="n">
-        <v>7.227170135593042e-05</v>
+        <v>2.702903649325333e-14</v>
       </c>
       <c r="CM7" t="n">
-        <v>9.910799417411909e-05</v>
+        <v>2.382973037103574e-14</v>
       </c>
       <c r="CN7" t="n">
-        <v>3.414204911678098e-05</v>
+        <v>8.309362719378585e-14</v>
       </c>
       <c r="CO7" t="n">
-        <v>6.764921636204235e-06</v>
+        <v>3.138465439682207e-14</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.0001010563937597908</v>
+        <v>3.856840519698979e-14</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0001817449956433848</v>
+        <v>5.737050374696184e-14</v>
       </c>
       <c r="CR7" t="n">
-        <v>5.930887709837407e-06</v>
+        <v>1.058583322182619e-14</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.0001789749367162585</v>
+        <v>1.045235184076723e-14</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.0001893126755021513</v>
+        <v>2.535413217807751e-14</v>
       </c>
       <c r="CU7" t="n">
-        <v>8.104082371573895e-05</v>
+        <v>3.210019056121283e-14</v>
       </c>
       <c r="CV7" t="n">
-        <v>5.652600520988926e-07</v>
+        <v>1.493739722570938e-14</v>
       </c>
       <c r="CW7" t="n">
-        <v>4.486743637244217e-05</v>
+        <v>1.014577080660738e-14</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.038693153532222e-05</v>
+        <v>7.371122958429836e-15</v>
       </c>
       <c r="CY7" t="n">
-        <v>3.838360134977847e-05</v>
+        <v>2.889251744754226e-14</v>
       </c>
       <c r="CZ7" t="n">
-        <v>7.23675184417516e-05</v>
+        <v>1.009958040592771e-14</v>
       </c>
       <c r="DA7" t="n">
-        <v>3.436733095441014e-06</v>
+        <v>2.492362598856962e-14</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.833466012612917e-05</v>
+        <v>3.015900195730984e-15</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.121325476560742e-05</v>
+        <v>2.849950347737868e-15</v>
       </c>
       <c r="DD7" t="n">
-        <v>5.940938353887759e-05</v>
+        <v>2.531985783689981e-14</v>
       </c>
       <c r="DE7" t="n">
-        <v>2.385974403296132e-05</v>
+        <v>2.366499940345372e-14</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.0001651606580708176</v>
+        <v>1.357178699122347e-14</v>
       </c>
       <c r="DG7" t="n">
-        <v>5.789603164885193e-06</v>
+        <v>3.938423683859903e-14</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.000230477744480595</v>
+        <v>1.28573528166971e-14</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.0001840328477555886</v>
+        <v>2.329343654267936e-14</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.0001161866748589091</v>
+        <v>3.459632889413547e-14</v>
       </c>
       <c r="DK7" t="n">
-        <v>8.480995893478394e-05</v>
+        <v>1.752747490061431e-14</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.0002449004969093949</v>
+        <v>2.313224786688276e-14</v>
       </c>
       <c r="DM7" t="n">
-        <v>9.581618360243738e-05</v>
+        <v>8.192310389364566e-15</v>
       </c>
       <c r="DN7" t="n">
-        <v>5.250086542218924e-05</v>
+        <v>5.89586303837244e-15</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.087971850211034e-05</v>
+        <v>8.682089403422473e-15</v>
       </c>
       <c r="DP7" t="n">
-        <v>6.45499094389379e-05</v>
+        <v>8.975415218990743e-15</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.0001112806785386056</v>
+        <v>5.530146991923092e-14</v>
       </c>
       <c r="DR7" t="n">
-        <v>2.912268610089086e-05</v>
+        <v>2.016807131455939e-14</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.0001123350957641378</v>
+        <v>5.585973578223907e-14</v>
       </c>
       <c r="DT7" t="n">
-        <v>2.916457378887571e-05</v>
+        <v>3.935294066526387e-14</v>
       </c>
       <c r="DU7" t="n">
-        <v>5.72453391214367e-05</v>
+        <v>9.931525681060663e-15</v>
       </c>
       <c r="DV7" t="n">
-        <v>5.687185876013245e-06</v>
+        <v>2.376680005821948e-15</v>
       </c>
       <c r="DW7" t="n">
-        <v>2.883636807382572e-05</v>
+        <v>4.206056618445697e-14</v>
       </c>
       <c r="DX7" t="n">
-        <v>1.783495463314466e-05</v>
+        <v>8.143133350512876e-15</v>
       </c>
       <c r="DY7" t="n">
-        <v>1.225905543833505e-05</v>
+        <v>5.462346493770006e-15</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.749064464704134e-05</v>
+        <v>1.81868561687339e-14</v>
       </c>
       <c r="EA7" t="n">
-        <v>8.580106623412576e-06</v>
+        <v>1.08418667178257e-14</v>
       </c>
       <c r="EB7" t="n">
-        <v>4.09580570703838e-05</v>
+        <v>8.958574509933433e-15</v>
       </c>
       <c r="EC7" t="n">
-        <v>4.25984944740776e-06</v>
+        <v>3.258046501856959e-14</v>
       </c>
       <c r="ED7" t="n">
-        <v>8.820519724395126e-05</v>
+        <v>2.579998491052376e-14</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.0001443234941689298</v>
+        <v>2.009581432196091e-14</v>
       </c>
       <c r="EF7" t="n">
-        <v>3.348636892042123e-05</v>
+        <v>1.181824074909278e-14</v>
       </c>
       <c r="EG7" t="n">
-        <v>2.815160041791387e-05</v>
+        <v>3.411452300121007e-14</v>
       </c>
       <c r="EH7" t="n">
-        <v>4.217611058265902e-05</v>
+        <v>1.894612464419139e-14</v>
       </c>
       <c r="EI7" t="n">
-        <v>6.492719694506377e-05</v>
+        <v>5.429337196299032e-14</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.0001051554208970629</v>
+        <v>9.950102807659844e-15</v>
       </c>
       <c r="EK7" t="n">
-        <v>1.436091679352103e-05</v>
+        <v>2.222056258883044e-14</v>
       </c>
       <c r="EL7" t="n">
-        <v>4.789172635355499e-06</v>
+        <v>1.544968952847236e-14</v>
       </c>
       <c r="EM7" t="n">
-        <v>9.988304373109713e-05</v>
+        <v>1.489899444594676e-14</v>
       </c>
       <c r="EN7" t="n">
-        <v>8.178957068594173e-05</v>
+        <v>3.382681301408209e-14</v>
       </c>
       <c r="EO7" t="n">
-        <v>4.339326551416889e-05</v>
+        <v>1.634714126487902e-14</v>
       </c>
       <c r="EP7" t="n">
-        <v>4.098680437891744e-05</v>
+        <v>4.134648691673549e-14</v>
       </c>
       <c r="EQ7" t="n">
-        <v>3.943515184801072e-05</v>
+        <v>5.431449696469484e-14</v>
       </c>
       <c r="ER7" t="n">
-        <v>1.371327743981965e-05</v>
+        <v>4.843877340519279e-15</v>
       </c>
       <c r="ES7" t="n">
-        <v>2.488034078851342e-05</v>
+        <v>1.031807933093553e-14</v>
       </c>
       <c r="ET7" t="n">
-        <v>9.084574412554502e-05</v>
+        <v>4.097251848239093e-14</v>
       </c>
       <c r="EU7" t="n">
-        <v>9.195864549838006e-07</v>
+        <v>3.399455941895634e-14</v>
       </c>
       <c r="EV7" t="n">
-        <v>6.946093344595283e-05</v>
+        <v>1.60193429024234e-14</v>
       </c>
       <c r="EW7" t="n">
-        <v>3.66692001989577e-05</v>
+        <v>1.963969555019394e-14</v>
       </c>
       <c r="EX7" t="n">
-        <v>1.152216282207519e-05</v>
+        <v>2.573195630639798e-14</v>
       </c>
       <c r="EY7" t="n">
-        <v>4.710896610049531e-05</v>
+        <v>1.768075059461766e-14</v>
       </c>
       <c r="EZ7" t="n">
-        <v>2.822270653268788e-05</v>
+        <v>1.770520951800258e-14</v>
       </c>
       <c r="FA7" t="n">
-        <v>4.945281762047671e-05</v>
+        <v>2.670410279622532e-14</v>
       </c>
       <c r="FB7" t="n">
-        <v>6.353040225803852e-05</v>
+        <v>4.462214882398332e-15</v>
       </c>
       <c r="FC7" t="n">
-        <v>1.6806519624879e-06</v>
+        <v>2.936859739774422e-14</v>
       </c>
       <c r="FD7" t="n">
-        <v>2.674452389328508e-06</v>
+        <v>1.377096001250674e-14</v>
       </c>
       <c r="FE7" t="n">
-        <v>2.730073720158543e-05</v>
+        <v>5.226152626977565e-15</v>
       </c>
       <c r="FF7" t="n">
-        <v>3.934617052436806e-05</v>
+        <v>2.924799345858237e-14</v>
       </c>
       <c r="FG7" t="n">
-        <v>1.865004378487356e-05</v>
+        <v>8.18747196776326e-14</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.000108752072264906</v>
+        <v>1.864544150044327e-14</v>
       </c>
       <c r="FI7" t="n">
-        <v>2.804469841066748e-05</v>
+        <v>2.498787174355296e-14</v>
       </c>
       <c r="FJ7" t="n">
-        <v>1.115277700591832e-05</v>
+        <v>1.419110021280614e-14</v>
       </c>
       <c r="FK7" t="n">
-        <v>8.358462218893692e-05</v>
+        <v>1.668987451226064e-14</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.0001321167219430208</v>
+        <v>3.941615981631515e-14</v>
       </c>
       <c r="FM7" t="n">
-        <v>1.016870737657882e-05</v>
+        <v>3.446857599689879e-14</v>
       </c>
       <c r="FN7" t="n">
-        <v>4.249820995028131e-05</v>
+        <v>1.688673174546611e-14</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.000176346700754948</v>
+        <v>4.053132612522048e-14</v>
       </c>
       <c r="FP7" t="n">
-        <v>2.889702955144458e-05</v>
+        <v>7.769226749573463e-15</v>
       </c>
       <c r="FQ7" t="n">
-        <v>2.549450618971605e-05</v>
+        <v>3.911860730634008e-14</v>
       </c>
       <c r="FR7" t="n">
-        <v>1.386293661198579e-06</v>
+        <v>1.511784404259475e-14</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.0001376419386360794</v>
+        <v>7.438863571353552e-15</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.0003150927368551493</v>
+        <v>4.508170909061499e-14</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.0001302893506363034</v>
+        <v>4.993184685164742e-14</v>
       </c>
       <c r="FV7" t="n">
-        <v>9.848846093518659e-05</v>
+        <v>5.66826045735741e-14</v>
       </c>
       <c r="FW7" t="n">
-        <v>7.349438419623766e-06</v>
+        <v>5.403818211180628e-15</v>
       </c>
       <c r="FX7" t="n">
-        <v>5.020857861381955e-05</v>
+        <v>1.454527348717337e-14</v>
       </c>
       <c r="FY7" t="n">
-        <v>3.388127151993103e-05</v>
+        <v>1.524988631467633e-14</v>
       </c>
       <c r="FZ7" t="n">
-        <v>9.083081386052072e-05</v>
+        <v>1.974702140087464e-14</v>
       </c>
       <c r="GA7" t="n">
-        <v>9.934198169503361e-05</v>
+        <v>1.037743262361553e-15</v>
       </c>
       <c r="GB7" t="n">
-        <v>5.643557233270258e-05</v>
+        <v>3.517092894049847e-14</v>
       </c>
       <c r="GC7" t="n">
-        <v>4.818571687792428e-05</v>
+        <v>4.670028740886428e-14</v>
       </c>
       <c r="GD7" t="n">
-        <v>9.485910413786769e-05</v>
+        <v>4.966716260815761e-14</v>
       </c>
       <c r="GE7" t="n">
-        <v>6.436021067202091e-07</v>
+        <v>9.786948168392668e-15</v>
       </c>
       <c r="GF7" t="n">
-        <v>2.05203250516206e-05</v>
+        <v>2.375694652394407e-14</v>
       </c>
       <c r="GG7" t="n">
-        <v>8.140776481013745e-05</v>
+        <v>1.218817391847662e-14</v>
       </c>
     </row>
     <row r="8">
@@ -4982,3416 +4982,3416 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.08997548371553421</v>
+        <v>0.1106379330158234</v>
       </c>
       <c r="B9" t="n">
-        <v>1.15679395198822</v>
+        <v>0.1851276755332947</v>
       </c>
       <c r="C9" t="n">
-        <v>0.103847861289978</v>
+        <v>0.04257422685623169</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6582435965538025</v>
+        <v>0.09345359355211258</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06920356303453445</v>
+        <v>0.1312066316604614</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2171415388584137</v>
+        <v>0.2086759656667709</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02099280059337616</v>
+        <v>0.1794780045747757</v>
       </c>
       <c r="H9" t="n">
-        <v>0.07784314453601837</v>
+        <v>0.2396836578845978</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06795477867126465</v>
+        <v>0.03774525970220566</v>
       </c>
       <c r="J9" t="n">
-        <v>0.195194199681282</v>
+        <v>0.1736116111278534</v>
       </c>
       <c r="K9" t="n">
-        <v>0.864547073841095</v>
+        <v>0.06036330014467239</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02308953553438187</v>
+        <v>0.01779738813638687</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6232105493545532</v>
+        <v>0.2869299054145813</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05902289599180222</v>
+        <v>0.3773775994777679</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2939561009407043</v>
+        <v>0.2535929977893829</v>
       </c>
       <c r="P9" t="n">
-        <v>0.009552836418151855</v>
+        <v>0.2798207998275757</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1121358200907707</v>
+        <v>0.2605700492858887</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1584781557321548</v>
+        <v>0.050466638058424</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03312503546476364</v>
+        <v>0.05378701537847519</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1354034543037415</v>
+        <v>0.01965361461043358</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02540549635887146</v>
+        <v>0.1234833151102066</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1470122486352921</v>
+        <v>0.06859650462865829</v>
       </c>
       <c r="W9" t="n">
-        <v>0.09137284010648727</v>
+        <v>0.0804615318775177</v>
       </c>
       <c r="X9" t="n">
-        <v>0.06875010579824448</v>
+        <v>0.009005086496472359</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.05965088307857513</v>
+        <v>0.004036983475089073</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.11574437469244</v>
+        <v>0.07914304733276367</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.1001925766468048</v>
+        <v>0.05137765407562256</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03092126548290253</v>
+        <v>0.0010449931723997</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1471665352582932</v>
+        <v>0.08554719388484955</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0817672461271286</v>
+        <v>0.06699293851852417</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0744505375623703</v>
+        <v>0.001477120444178581</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.01396300364285707</v>
+        <v>0.1478421986103058</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.07613180577754974</v>
+        <v>0.04556797444820404</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.03625785559415817</v>
+        <v>0.01705643534660339</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.02078508213162422</v>
+        <v>0.122386060655117</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.1218969821929932</v>
+        <v>0.0350448340177536</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.04300966113805771</v>
+        <v>0.01459423266351223</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.1431825906038284</v>
+        <v>0.1473435759544373</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.00147554068826139</v>
+        <v>0.1737643480300903</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.06776319444179535</v>
+        <v>0.04233855009078979</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.02364145591855049</v>
+        <v>0.05092235282063484</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.1338958889245987</v>
+        <v>0.003901629708707333</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.02829652279615402</v>
+        <v>0.03969140350818634</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.1097920686006546</v>
+        <v>0.007493006065487862</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.08563712239265442</v>
+        <v>0.05121250823140144</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.1044545695185661</v>
+        <v>0.004746347665786743</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.7708972692489624</v>
+        <v>0.01658150181174278</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.05029379948973656</v>
+        <v>0.1586677134037018</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.07905593514442444</v>
+        <v>0.01965454965829849</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.1685528755187988</v>
+        <v>0.4251407980918884</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.03512432426214218</v>
+        <v>0.1930169016122818</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.01470302045345306</v>
+        <v>0.05549668520689011</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.05243999511003494</v>
+        <v>0.03765036165714264</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.1206369772553444</v>
+        <v>0.04869844764471054</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.06987171620130539</v>
+        <v>0.05681947991251945</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.193735659122467</v>
+        <v>0.09672129154205322</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.1785349100828171</v>
+        <v>0.01152922585606575</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.1493870615959167</v>
+        <v>0.03353274613618851</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.2918677031993866</v>
+        <v>0.1196770519018173</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.1227160468697548</v>
+        <v>0.04948224499821663</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.09906609356403351</v>
+        <v>0.01763210259377956</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.201215073466301</v>
+        <v>0.1063557490706444</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.01813588850200176</v>
+        <v>0.01495296228677034</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.1230483800172806</v>
+        <v>0.04387139901518822</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.1585643440485001</v>
+        <v>0.06108057126402855</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.07514667510986328</v>
+        <v>0.01633784547448158</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.05937808752059937</v>
+        <v>0.06503156572580338</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.04977705329656601</v>
+        <v>0.01864339783787727</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.03799596428871155</v>
+        <v>0.07632531225681305</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.03826937824487686</v>
+        <v>0.0181944202631712</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.003082389011979103</v>
+        <v>0.01168288290500641</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.02636671625077724</v>
+        <v>0.01530919782817364</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.1171811819076538</v>
+        <v>0.03129885345697403</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.3904514908790588</v>
+        <v>0.03902767226099968</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.05474942922592163</v>
+        <v>0.1208933889865875</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.09678816795349121</v>
+        <v>0.1484167873859406</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.09575688093900681</v>
+        <v>0.1450665146112442</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.1241270899772644</v>
+        <v>0.09308552742004395</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.01123357564210892</v>
+        <v>0.0437343642115593</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.0155233945697546</v>
+        <v>0.03747322410345078</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.1708547174930573</v>
+        <v>0.04278378933668137</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.07330568879842758</v>
+        <v>0.03815338015556335</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.1960849165916443</v>
+        <v>0.02811596542596817</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.07038938254117966</v>
+        <v>0.03467829525470734</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.08511055260896683</v>
+        <v>0.05454660207033157</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.083542600274086</v>
+        <v>0.02587244659662247</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.01707609929144382</v>
+        <v>0.06301536411046982</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.05877265334129333</v>
+        <v>0.02019582875072956</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.006366695277392864</v>
+        <v>0.05129402503371239</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.05859801918268204</v>
+        <v>0.04606876149773598</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.1139376014471054</v>
+        <v>0.01782578602433205</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.03579162433743477</v>
+        <v>0.06326962262392044</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.0475713312625885</v>
+        <v>0.1643271446228027</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.2015437036752701</v>
+        <v>0.1806037724018097</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.08413589745759964</v>
+        <v>0.1314046680927277</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.1336808800697327</v>
+        <v>0.1323082000017166</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.1449456810951233</v>
+        <v>0.05693385377526283</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.2079987525939941</v>
+        <v>0.03073451109230518</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.004520618356764317</v>
+        <v>0.04843512177467346</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.07161751389503479</v>
+        <v>0.05197107419371605</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.1678473502397537</v>
+        <v>0.01363495364785194</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.08427726477384567</v>
+        <v>0.02457909658551216</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.1298496574163437</v>
+        <v>0.06855092942714691</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.07694432139396667</v>
+        <v>0.06702432036399841</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.03025693818926811</v>
+        <v>0.0747775062918663</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.06716178357601166</v>
+        <v>0.03885579481720924</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.03780999034643173</v>
+        <v>0.06100817397236824</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.02538611739873886</v>
+        <v>0.05092431604862213</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.007740095257759094</v>
+        <v>0.03130976483225822</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.2363511025905609</v>
+        <v>0.04323333501815796</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.01445748377591372</v>
+        <v>0.01664956286549568</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.2974465787410736</v>
+        <v>0.04170046374201775</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.1285449266433716</v>
+        <v>0.01358943991363049</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.1537384688854218</v>
+        <v>0.2867361903190613</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.092966228723526</v>
+        <v>0.0306922048330307</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.04226754605770111</v>
+        <v>0.0681084543466568</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.01196192763745785</v>
+        <v>0.2022280991077423</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.1129098758101463</v>
+        <v>0.09014279395341873</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.08399096876382828</v>
+        <v>0.07504922896623611</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.0494082123041153</v>
+        <v>0.02485348656773567</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.08949765563011169</v>
+        <v>0.007670445367693901</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.09322593361139297</v>
+        <v>0.08485804498195648</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.1069483384490013</v>
+        <v>0.08652474731206894</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.01271151565015316</v>
+        <v>0.06144390255212784</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.01379648968577385</v>
+        <v>0.1645004749298096</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.1244880706071854</v>
+        <v>0.03264954313635826</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.02273738756775856</v>
+        <v>0.02775050513446331</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.02970756590366364</v>
+        <v>0.06412964314222336</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.1266438663005829</v>
+        <v>0.1258242428302765</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.01799977011978626</v>
+        <v>0.08783318102359772</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.1112480312585831</v>
+        <v>0.09768787771463394</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.09450477361679077</v>
+        <v>0.2244849354028702</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.03585213795304298</v>
+        <v>0.02516365237534046</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.009244201704859734</v>
+        <v>0.05660712346434593</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.008024320937693119</v>
+        <v>0.04762101918458939</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.03296957910060883</v>
+        <v>0.06096837297081947</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.1092953830957413</v>
+        <v>0.0577271357178688</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.04265301674604416</v>
+        <v>0.1131215766072273</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.03478123620152473</v>
+        <v>0.05868256837129593</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.008504138328135014</v>
+        <v>0.02986443601548672</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.03117844648659229</v>
+        <v>0.04829250276088715</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.02351208962500095</v>
+        <v>0.007646715268492699</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.02374177426099777</v>
+        <v>0.003223201259970665</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.03158041462302208</v>
+        <v>0.05351021140813828</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.0213932953774929</v>
+        <v>0.04925695061683655</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.1447483599185944</v>
+        <v>0.09677845984697342</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.03137122094631195</v>
+        <v>0.05900959670543671</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.1217961758375168</v>
+        <v>0.0644528940320015</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.1025529727339745</v>
+        <v>0.06513594090938568</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.2589932084083557</v>
+        <v>0.06439420580863953</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.1480181217193604</v>
+        <v>0.0060729687102139</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.06798567622900009</v>
+        <v>0.0975271612405777</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.02345471829175949</v>
+        <v>0.01289865560829639</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.05374987423419952</v>
+        <v>0.04937527701258659</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.1676451414823532</v>
+        <v>0.02783414721488953</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.05447161942720413</v>
+        <v>0.02873725071549416</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.1156091541051865</v>
+        <v>0.06775812059640884</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.07650930434465408</v>
+        <v>0.03276763111352921</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.03642376139760017</v>
+        <v>0.05379601940512657</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.09392347186803818</v>
+        <v>0.03243175148963928</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.02336199767887592</v>
+        <v>0.0651702955365181</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.05820013955235481</v>
+        <v>0.01802418008446693</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.02229470014572144</v>
+        <v>0.05201409012079239</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.09631119668483734</v>
+        <v>0.01805046387016773</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.03044899553060532</v>
+        <v>0.04142483696341515</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.07229461520910263</v>
+        <v>0.01394427940249443</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.06761379539966583</v>
+        <v>0.06102634593844414</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.03144336119294167</v>
+        <v>0.002132069319486618</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.04448575153946877</v>
+        <v>0.009090342558920383</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.01129915844649076</v>
+        <v>0.1764190495014191</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.01192854065448046</v>
+        <v>0.06951917707920074</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.001693788915872574</v>
+        <v>0.1839017868041992</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.008375413715839386</v>
+        <v>0.139953538775444</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.2350569069385529</v>
+        <v>0.2765849828720093</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.1435184180736542</v>
+        <v>0.08792498707771301</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.0478346012532711</v>
+        <v>0.2207301408052444</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.0211084745824337</v>
+        <v>0.00681220181286335</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.06600868701934814</v>
+        <v>0.1714039146900177</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.0605328269302845</v>
+        <v>0.2125232219696045</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.06039654463529587</v>
+        <v>0.1404071301221848</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.1060654297471046</v>
+        <v>0.02678897231817245</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.06648171693086624</v>
+        <v>0.1444960236549377</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.0148628382012248</v>
+        <v>0.06848503649234772</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.02181955054402351</v>
+        <v>0.009480763226747513</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.1707782000303268</v>
+        <v>0.1235254406929016</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.1737635284662247</v>
+        <v>0.1318100094795227</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.3744415938854218</v>
+        <v>0.01100206188857555</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.08553112298250198</v>
+        <v>0.0484921783208847</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.04158582165837288</v>
+        <v>0.1085278168320656</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.008429328911006451</v>
+        <v>0.007433891296386719</v>
       </c>
       <c r="B10" t="n">
-        <v>0.3957622051239014</v>
+        <v>0.3865958452224731</v>
       </c>
       <c r="C10" t="n">
-        <v>0.04438538104295731</v>
+        <v>0.04656143486499786</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2953601479530334</v>
+        <v>0.005209706723690033</v>
       </c>
       <c r="E10" t="n">
-        <v>0.188230112195015</v>
+        <v>0.0398375503718853</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1332545578479767</v>
+        <v>0.0397583395242691</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1276305466890335</v>
+        <v>0.2183447480201721</v>
       </c>
       <c r="H10" t="n">
-        <v>0.09927080571651459</v>
+        <v>0.2221088856458664</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07978633046150208</v>
+        <v>0.1802856922149658</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01304169371724129</v>
+        <v>0.1683746874332428</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3465816974639893</v>
+        <v>0.3176188170909882</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05583749711513519</v>
+        <v>0.1123552545905113</v>
       </c>
       <c r="M10" t="n">
-        <v>0.245849072933197</v>
+        <v>0.25694739818573</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2078965753316879</v>
+        <v>0.4975035786628723</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1482371091842651</v>
+        <v>0.1457803547382355</v>
       </c>
       <c r="P10" t="n">
-        <v>0.03384116291999817</v>
+        <v>0.3385592699050903</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0249582938849926</v>
+        <v>0.1537848114967346</v>
       </c>
       <c r="R10" t="n">
-        <v>0.05901647731661797</v>
+        <v>0.3449251651763916</v>
       </c>
       <c r="S10" t="n">
-        <v>0.025348836556077</v>
+        <v>0.07729873061180115</v>
       </c>
       <c r="T10" t="n">
-        <v>0.03319138288497925</v>
+        <v>0.2099923342466354</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0205821730196476</v>
+        <v>0.03068684041500092</v>
       </c>
       <c r="V10" t="n">
-        <v>0.06385506689548492</v>
+        <v>0.2066662609577179</v>
       </c>
       <c r="W10" t="n">
-        <v>0.09119900315999985</v>
+        <v>0.1950340270996094</v>
       </c>
       <c r="X10" t="n">
-        <v>0.02306817471981049</v>
+        <v>0.06901295483112335</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.03579134494066238</v>
+        <v>0.05696319416165352</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01039371639490128</v>
+        <v>0.06812194734811783</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.008046926930546761</v>
+        <v>0.04477615654468536</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.03819636255502701</v>
+        <v>0.1852886378765106</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.02502340450882912</v>
+        <v>0.1589450538158417</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0258569810539484</v>
+        <v>0.008360046893358231</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.03105966374278069</v>
+        <v>0.159039169549942</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.01730479300022125</v>
+        <v>0.008052363991737366</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.008232492953538895</v>
+        <v>0.01291194558143616</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.03598050400614738</v>
+        <v>0.1301598846912384</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.05079012364149094</v>
+        <v>0.01012326776981354</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.05423007532954216</v>
+        <v>0.1408067643642426</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.03387720137834549</v>
+        <v>0.03645527362823486</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.09647420793771744</v>
+        <v>0.2576579451560974</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.03115599043667316</v>
+        <v>0.001540828496217728</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.01672058925032616</v>
+        <v>0.03734960407018661</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.008905012160539627</v>
+        <v>0.2438199818134308</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.05271907150745392</v>
+        <v>0.04652184620499611</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.01327121164649725</v>
+        <v>0.09666846692562103</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.06899232417345047</v>
+        <v>0.08348046243190765</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.003798599354922771</v>
+        <v>0.07587303221225739</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.02955295145511627</v>
+        <v>0.05589507520198822</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.3034734725952148</v>
+        <v>0.4593688249588013</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.01309499610215425</v>
+        <v>0.05516152083873749</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.1478096693754196</v>
+        <v>0.08124934136867523</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1249841302633286</v>
+        <v>0.3608837127685547</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.03178978711366653</v>
+        <v>0.1066004633903503</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.01036706753075123</v>
+        <v>0.490412175655365</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.02542684972286224</v>
+        <v>0.2445225715637207</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.02551585808396339</v>
+        <v>0.0443178117275238</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.04007384181022644</v>
+        <v>0.02520356327295303</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.1066266521811485</v>
+        <v>0.1866675615310669</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.03670872375369072</v>
+        <v>0.08150754123926163</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.04887903109192848</v>
+        <v>0.1073982417583466</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.1629660725593567</v>
+        <v>0.4142038524150848</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.0544116273522377</v>
+        <v>0.2035549432039261</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.04516196250915527</v>
+        <v>0.251429945230484</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.02357471361756325</v>
+        <v>0.1397552341222763</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.0005470328032970428</v>
+        <v>0.1384382098913193</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.07183847576379776</v>
+        <v>0.05668066442012787</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.03614643961191177</v>
+        <v>0.2148839235305786</v>
       </c>
       <c r="BN10" t="n">
-        <v>3.467965871095657e-05</v>
+        <v>0.05047821626067162</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.06826527416706085</v>
+        <v>0.1365462392568588</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.05413851141929626</v>
+        <v>0.1921293437480927</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.008373133838176727</v>
+        <v>0.03121073730289936</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.005745014175772667</v>
+        <v>0.002983963117003441</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.002634142991155386</v>
+        <v>0.08570779114961624</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.005688955076038837</v>
+        <v>0.03791771084070206</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.03741390258073807</v>
+        <v>0.1022381410002708</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.1731658130884171</v>
+        <v>0.2830218374729156</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.01858343929052353</v>
+        <v>0.02922794595360756</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.0777171328663826</v>
+        <v>0.5004511475563049</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.06352365761995316</v>
+        <v>0.3064068555831909</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.02939945459365845</v>
+        <v>0.0406571552157402</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.04521843791007996</v>
+        <v>0.28399458527565</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.01898651383817196</v>
+        <v>0.1087055802345276</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.0236552320420742</v>
+        <v>0.04083821550011635</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.03448443859815598</v>
+        <v>0.03284648805856705</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.03930399566888809</v>
+        <v>0.1455191522836685</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.01163506042212248</v>
+        <v>0.006042336579412222</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.05719022825360298</v>
+        <v>0.03542166575789452</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.006987798027694225</v>
+        <v>0.02058339677751064</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.03561276197433472</v>
+        <v>0.02636258490383625</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.007351289503276348</v>
+        <v>0.09359151124954224</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.01802259311079979</v>
+        <v>0.08356834948062897</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.003018485382199287</v>
+        <v>0.04019511118531227</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.0436132438480854</v>
+        <v>0.1778490394353867</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.03925419598817825</v>
+        <v>0.07235568761825562</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.01458512526005507</v>
+        <v>0.2601368427276611</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.008515097200870514</v>
+        <v>0.5644038319587708</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.08429094403982162</v>
+        <v>0.8869228363037109</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.005571629852056503</v>
+        <v>0.2141708731651306</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.09586174786090851</v>
+        <v>0.1977975368499756</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.05594231560826302</v>
+        <v>0.2315716296434402</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.008432157337665558</v>
+        <v>0.1054940298199654</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.02744102291762829</v>
+        <v>0.07394170761108398</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.02940187603235245</v>
+        <v>0.1349002420902252</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.01772833615541458</v>
+        <v>0.02565687336027622</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.0538838654756546</v>
+        <v>0.06398537755012512</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.02745296061038971</v>
+        <v>0.0161178782582283</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.04505589604377747</v>
+        <v>0.04515562951564789</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.005418460816144943</v>
+        <v>0.07829378545284271</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.01828075014054775</v>
+        <v>0.04926546663045883</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.01193362288177013</v>
+        <v>0.01139937900006771</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.0227029100060463</v>
+        <v>0.03074712306261063</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.01484110578894615</v>
+        <v>0.1187148168683052</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.09719344228506088</v>
+        <v>0.1024661362171173</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.1602008938789368</v>
+        <v>0.1005315631628036</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.04793218150734901</v>
+        <v>0.3083275556564331</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.03648204728960991</v>
+        <v>0.1621933281421661</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.08534342050552368</v>
+        <v>0.3207705020904541</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.03767608851194382</v>
+        <v>0.2183345705270767</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.01863849721848965</v>
+        <v>0.2512923777103424</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.07025942206382751</v>
+        <v>0.2360236048698425</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.05421856045722961</v>
+        <v>0.01332004182040691</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.05152244120836258</v>
+        <v>0.09598112106323242</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.0757916122674942</v>
+        <v>0.2477568686008453</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.001134156249463558</v>
+        <v>0.02643685787916183</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.02086693421006203</v>
+        <v>0.1167517527937889</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.0241041574627161</v>
+        <v>0.009762836620211601</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.08596711605787277</v>
+        <v>0.03992540016770363</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.03783532977104187</v>
+        <v>0.006278908345848322</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.02285583131015301</v>
+        <v>0.02228543534874916</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.03419134393334389</v>
+        <v>0.03312231600284576</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.05244814231991768</v>
+        <v>0.08335950970649719</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.04386544972658157</v>
+        <v>0.04197052121162415</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.0838327631354332</v>
+        <v>0.04301881045103073</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.07078268378973007</v>
+        <v>0.04258370399475098</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.0329311192035675</v>
+        <v>0.2624427080154419</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.01252071093767881</v>
+        <v>0.04005174338817596</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.006852420046925545</v>
+        <v>0.1552489101886749</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.006947486661374569</v>
+        <v>0.04208263009786606</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.02421117946505547</v>
+        <v>0.02204668149352074</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.01560148503631353</v>
+        <v>0.04061479493975639</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.05408505350351334</v>
+        <v>0.1860354244709015</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.02730771154165268</v>
+        <v>0.08220368623733521</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.03087959252297878</v>
+        <v>0.09959776699542999</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.0008886675350368023</v>
+        <v>0.02571555972099304</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.003646179102361202</v>
+        <v>0.03766689822077751</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.02566622756421566</v>
+        <v>0.08290497958660126</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.005093052983283997</v>
+        <v>0.2339432835578918</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.02031906694173813</v>
+        <v>0.13400898873806</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.002858664374798536</v>
+        <v>0.08739833533763885</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.02808396704494953</v>
+        <v>0.1005774289369583</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.008403033018112183</v>
+        <v>0.01771876215934753</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.1070145666599274</v>
+        <v>0.05909037590026855</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.0006092935218475759</v>
+        <v>0.01253928616642952</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.1358470618724823</v>
+        <v>0.06433458626270294</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.04669708758592606</v>
+        <v>0.1313461661338806</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.03499986231327057</v>
+        <v>0.02861927822232246</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.02983424440026283</v>
+        <v>0.1276998817920685</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.007376995868980885</v>
+        <v>0.04201528429985046</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.05187550932168961</v>
+        <v>0.09452372789382935</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.02702686563134193</v>
+        <v>0.08512247353792191</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.03596629947423935</v>
+        <v>0.01310641691088676</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.02138524688780308</v>
+        <v>0.08135050535202026</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.02068667858839035</v>
+        <v>0.08518503606319427</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.01398213673382998</v>
+        <v>0.03449343517422676</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.001341254450380802</v>
+        <v>0.008377129212021828</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.09344039857387543</v>
+        <v>0.2125576734542847</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.01213874015957117</v>
+        <v>0.02214768901467323</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.05251489207148552</v>
+        <v>0.06170479953289032</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.04257438704371452</v>
+        <v>0.01072605699300766</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.06608027219772339</v>
+        <v>0.1160254329442978</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.0004779002629220486</v>
+        <v>0.03333934396505356</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.03536960110068321</v>
+        <v>0.08889353275299072</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.02923078462481499</v>
+        <v>0.05702722817659378</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.02569510787725449</v>
+        <v>0.09755893796682358</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.1189647614955902</v>
+        <v>0.5445781946182251</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.04132751375436783</v>
+        <v>0.2379566878080368</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.03688798472285271</v>
+        <v>0.3825814127922058</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.09314431250095367</v>
+        <v>0.3507019281387329</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.0306034442037344</v>
+        <v>0.2873347997665405</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.1758018434047699</v>
+        <v>0.4709216952323914</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.01130986213684082</v>
+        <v>0.3416696190834045</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.03959622979164124</v>
+        <v>0.0231204554438591</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.0371122807264328</v>
+        <v>0.07990375906229019</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.03572015836834908</v>
+        <v>0.09038881957530975</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.03809759020805359</v>
+        <v>0.125930979847908</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.006883874535560608</v>
+        <v>0.120012030005455</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.1258552670478821</v>
+        <v>0.06206527352333069</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.0244066808372736</v>
+        <v>0.2954957187175751</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.1543981581926346</v>
+        <v>0.02871813997626305</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.02983886003494263</v>
+        <v>0.008635364472866058</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.02762291952967644</v>
+        <v>0.04819779843091965</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.007457135245203972</v>
+        <v>0.001502790721133351</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1789000481367111</v>
+        <v>0.0112249031662941</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01601158082485199</v>
+        <v>0.002461107447743416</v>
       </c>
       <c r="D11" t="n">
-        <v>0.08351638168096542</v>
+        <v>0.002803223207592964</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02818712033331394</v>
+        <v>0.0006597798783332109</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01001901365816593</v>
+        <v>0.002372676972299814</v>
       </c>
       <c r="G11" t="n">
-        <v>0.009215174242854118</v>
+        <v>0.001089815748855472</v>
       </c>
       <c r="H11" t="n">
-        <v>0.003787009045481682</v>
+        <v>0.0007065616082400084</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02962175011634827</v>
+        <v>0.003008454805240035</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01320460718125105</v>
+        <v>0.0002873925259336829</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1508117020130157</v>
+        <v>0.01198351010680199</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002616343321278691</v>
+        <v>0.003710546530783176</v>
       </c>
       <c r="M11" t="n">
-        <v>0.07487542182207108</v>
+        <v>0.005191233940422535</v>
       </c>
       <c r="N11" t="n">
-        <v>0.03786699846386909</v>
+        <v>0.001242679078131914</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02444000914692879</v>
+        <v>0.001292088418267667</v>
       </c>
       <c r="P11" t="n">
-        <v>0.009911941364407539</v>
+        <v>0.001219906727783382</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.03553329780697823</v>
+        <v>0.000813793099950999</v>
       </c>
       <c r="R11" t="n">
-        <v>0.02303017675876617</v>
+        <v>0.003008551429957151</v>
       </c>
       <c r="S11" t="n">
-        <v>0.003566171042621136</v>
+        <v>0.0002464152057655156</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01949814148247242</v>
+        <v>0.001765396213158965</v>
       </c>
       <c r="U11" t="n">
-        <v>0.005741007626056671</v>
+        <v>0.0005075964145362377</v>
       </c>
       <c r="V11" t="n">
-        <v>0.01233848556876183</v>
+        <v>0.0006666788831353188</v>
       </c>
       <c r="W11" t="n">
-        <v>0.002400015015155077</v>
+        <v>0.0007027094252407551</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01397731434553862</v>
+        <v>0.002093758434057236</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01957600377500057</v>
+        <v>0.0009797133971005678</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.01994599960744381</v>
+        <v>0.0003865036997012794</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.01387559343129396</v>
+        <v>0.002279817126691341</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.009975298307836056</v>
+        <v>0.001612783293239772</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.01979105919599533</v>
+        <v>0.0001120272791013122</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.003068311139941216</v>
+        <v>7.768895738990977e-05</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.01139701809734106</v>
+        <v>0.002352322917431593</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.01335688680410385</v>
+        <v>0.00151557638309896</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.001206244807690382</v>
+        <v>0.001647275639697909</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.001934826956130564</v>
+        <v>0.0006724749109707773</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0090614203363657</v>
+        <v>0.002005843911319971</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.003662290750071406</v>
+        <v>0.001689588883891702</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.01651391945779324</v>
+        <v>0.0002185169141739607</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.005445914342999458</v>
+        <v>0.002292697783559561</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.001240345183759928</v>
+        <v>0.0007653333013877273</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.01560288388282061</v>
+        <v>0.001226319000124931</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.02073894068598747</v>
+        <v>0.0006492471438832581</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.01594763621687889</v>
+        <v>0.001019618473947048</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.007511297706514597</v>
+        <v>0.0002806011179927737</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.007206584792584181</v>
+        <v>0.0008476946386508644</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.006971886847168207</v>
+        <v>0.0007481072098016739</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.005591542925685644</v>
+        <v>0.0005011187749914825</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.1085286065936089</v>
+        <v>0.007063223049044609</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.02285033278167248</v>
+        <v>4.77334251627326e-05</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.03107428923249245</v>
+        <v>0.0007000663317739964</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.00535159558057785</v>
+        <v>0.005042340606451035</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.01861170865595341</v>
+        <v>0.001765051274560392</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.00582207553088665</v>
+        <v>0.0004733584937639534</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.01702924072742462</v>
+        <v>0.001781350700184703</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.0004066701512783766</v>
+        <v>0.00192490906920284</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.008337787352502346</v>
+        <v>0.001100854598917067</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.02154269255697727</v>
+        <v>5.486662848852575e-05</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.04194677993655205</v>
+        <v>0.001601101364940405</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.006187858060002327</v>
+        <v>0.002050292678177357</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.03167171776294708</v>
+        <v>0.001058303634636104</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.00877456646412611</v>
+        <v>0.0007477601175196469</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.009153628721833229</v>
+        <v>0.0002545358438510448</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.02316731214523315</v>
+        <v>0.001915214583277702</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.01554322056472301</v>
+        <v>0.0004686021711677313</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.005282478872686625</v>
+        <v>0.0001363959454465657</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.01339435670524836</v>
+        <v>0.0007198830717243254</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.0111958272755146</v>
+        <v>0.001106051146052778</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.003093198407441378</v>
+        <v>0.0003168151306454092</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.01907682418823242</v>
+        <v>0.00111341814044863</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.016643226146698</v>
+        <v>0.0003328221500851214</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.01704474166035652</v>
+        <v>0.0003448131319601089</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.007429727353155613</v>
+        <v>0.0005677547305822372</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.007602252066135406</v>
+        <v>0.0003325082652736455</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.009706303477287292</v>
+        <v>0.0006503254408016801</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.05815840512514114</v>
+        <v>0.004767789039760828</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.01123555563390255</v>
+        <v>0.0009102831245400012</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.0123844500631094</v>
+        <v>0.001113610109314322</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.003525835927575827</v>
+        <v>0.0006892367964610457</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.015684949234128</v>
+        <v>0.002049501985311508</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.007344184443354607</v>
+        <v>0.001708304393105209</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.0002481159754097462</v>
+        <v>0.001018037903122604</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.002300925087183714</v>
+        <v>0.001366290263831615</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.006937652360647917</v>
+        <v>0.0002232992410426959</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.03152467310428619</v>
+        <v>0.003291385481134057</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.008628075011074543</v>
+        <v>0.001068659010343254</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.009726807475090027</v>
+        <v>0.001262531382963061</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.007110810372978449</v>
+        <v>0.0003909158403985202</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.006233538966625929</v>
+        <v>0.0004211050691083074</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.004039891064167023</v>
+        <v>0.0002039482351392508</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.00515745347365737</v>
+        <v>0.0005741192726418376</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.01028784271329641</v>
+        <v>0.0005477157537825406</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.0388002060353756</v>
+        <v>0.0002034081844612956</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.005622568540275097</v>
+        <v>0.00235690176486969</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.003168096533045173</v>
+        <v>0.001893131993710995</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.02707593888044357</v>
+        <v>0.004057419486343861</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.03233625739812851</v>
+        <v>0.003305700141936541</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.03689562529325485</v>
+        <v>0.001758930971845984</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.01943729817867279</v>
+        <v>0.0005399523070082068</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.01860949583351612</v>
+        <v>0.001278131501749158</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.02130999229848385</v>
+        <v>0.0009153197170235217</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.004158198833465576</v>
+        <v>0.0001583525445312262</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.03214510902762413</v>
+        <v>0.003070883685722947</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.0134529173374176</v>
+        <v>0.0009648741688579321</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.01587454602122307</v>
+        <v>0.001247349893674254</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.007989769801497459</v>
+        <v>9.649229468777776e-05</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.006141716614365578</v>
+        <v>0.0008637306746095419</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.003948039840906858</v>
+        <v>9.764006972545758e-05</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.00747004384174943</v>
+        <v>0.0002199878508690745</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.009976268745958805</v>
+        <v>0.001032424159348011</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.01976916939020157</v>
+        <v>0.0006738922093063593</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.02287727408111095</v>
+        <v>0.003456741105765104</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.0003236717311665416</v>
+        <v>0.0001043320662574843</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.03322626277804375</v>
+        <v>0.001626273151487112</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.02195900119841099</v>
+        <v>0.003125288523733616</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.01395484711974859</v>
+        <v>0.00312912161462009</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.01629623398184776</v>
+        <v>0.0009819688275456429</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.002597369253635406</v>
+        <v>2.045021392405033e-05</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.01930746249854565</v>
+        <v>4.910392453894019e-05</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.0142721738666296</v>
+        <v>0.0002248425153084099</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.008195037022233009</v>
+        <v>0.001335812266916037</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.001989349024370313</v>
+        <v>0.0007383170304819942</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.02384187094867229</v>
+        <v>0.000237325526541099</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.0152739156037569</v>
+        <v>0.0008765762322582304</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.008932309225201607</v>
+        <v>0.0005212544929236174</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.0003737462684512138</v>
+        <v>0.0008588103810325265</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.007381696254014969</v>
+        <v>0.001113690435886383</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.005260864272713661</v>
+        <v>0.0004583564586937428</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.007432731334120035</v>
+        <v>0.0002675470313988626</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.02481084503233433</v>
+        <v>4.153870395384729e-05</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.01493062172085047</v>
+        <v>0.0003455796977505088</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.008658681996166706</v>
+        <v>0.000984914368018508</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.01851237192749977</v>
+        <v>4.94962150696665e-05</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.00132352951914072</v>
+        <v>0.001633826061151922</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.02093680575489998</v>
+        <v>0.0003475197008810937</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.005204874556511641</v>
+        <v>0.002930682618170977</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.02004867978394032</v>
+        <v>0.001197668258100748</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.02558061107993126</v>
+        <v>7.50453255022876e-05</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.03318234533071518</v>
+        <v>0.003393765538930893</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.02101062051951885</v>
+        <v>0.0003956521686632186</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.01923731528222561</v>
+        <v>0.0008447377476841211</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.01636992394924164</v>
+        <v>1.9329774659127e-05</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.0001111488090828061</v>
+        <v>0.0009111046092584729</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.005599417258054018</v>
+        <v>0.0008800700306892395</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.0009817009558901191</v>
+        <v>0.0004749374929815531</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.005208642687648535</v>
+        <v>0.0006339664105325937</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.003229199443012476</v>
+        <v>0.0003951149410568178</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.0293596163392067</v>
+        <v>0.002849850337952375</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.00994175486266613</v>
+        <v>0.0004540052323136479</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.01225590333342552</v>
+        <v>0.000801841146312654</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.01012139953672886</v>
+        <v>0.0004004265647381544</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.0005130477948114276</v>
+        <v>0.001235036528669298</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.01462787669152021</v>
+        <v>0.0008460019016638398</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.003900503739714622</v>
+        <v>0.001005058409646153</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.001331477891653776</v>
+        <v>0.0001725514302961528</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.01007772795855999</v>
+        <v>0.0003828727058134973</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.03308990597724915</v>
+        <v>0.003805726766586304</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.009763605892658234</v>
+        <v>0.0008478339877910912</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.01053183153271675</v>
+        <v>0.001504006213508546</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.008438117802143097</v>
+        <v>1.590000465512276e-06</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.004962848033756018</v>
+        <v>0.0005461793043650687</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.003747751004993916</v>
+        <v>3.579538315534592e-06</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.004271337762475014</v>
+        <v>0.0006891445955261588</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.01226284727454185</v>
+        <v>0.0008140583522617817</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.006313055753707886</v>
+        <v>0.0008417349308729172</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.01239627413451672</v>
+        <v>0.001841509947553277</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.01507068518549204</v>
+        <v>0.0004700145800597966</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.01655486039817333</v>
+        <v>0.0007351269014179707</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.0227042268961668</v>
+        <v>0.0001827861415222287</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.008884364739060402</v>
+        <v>3.193318843841553e-05</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.005068022757768631</v>
+        <v>9.43073391681537e-05</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.0009955607820302248</v>
+        <v>0.0001529758446849883</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.001048322301357985</v>
+        <v>0.0009284797124564648</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.02583687752485275</v>
+        <v>0.001439780928194523</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.01378979161381721</v>
+        <v>0.0009730636375024915</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.03256133198738098</v>
+        <v>3.211211878806353e-05</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.003380917478352785</v>
+        <v>0.0007267586188390851</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.0006118006422184408</v>
+        <v>0.0038676792755723</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.008873189799487591</v>
+        <v>0.001207426423206925</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.02130208350718021</v>
+        <v>0.0009395547094754875</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.006467320024967194</v>
+        <v>0.0004570428282022476</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.02134433388710022</v>
+        <v>0.002234820742160082</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.01445801369845867</v>
+        <v>0.001451226184144616</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.003084091003984213</v>
+        <v>0.002315007150173187</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.008321916684508324</v>
+        <v>0.00135110504925251</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.0076902792789042</v>
+        <v>0.000299030973110348</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.001567204133607447</v>
+        <v>0.002341881394386292</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.01473963912576437</v>
+        <v>0.001261620549485087</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.01625972241163254</v>
+        <v>0.001236779731698334</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.01496610604226589</v>
+        <v>0.001054391032084823</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.02020231261849403</v>
+        <v>0.001058651367202401</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.00204048864543438</v>
+        <v>0.007901977747678757</v>
       </c>
       <c r="B12" t="n">
-        <v>0.02313845045864582</v>
+        <v>0.02896992862224579</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0003172686265315861</v>
+        <v>0.008783189579844475</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01797297969460487</v>
+        <v>0.007015752606093884</v>
       </c>
       <c r="E12" t="n">
-        <v>0.00418649148195982</v>
+        <v>0.007607481442391872</v>
       </c>
       <c r="F12" t="n">
-        <v>0.004857760388404131</v>
+        <v>0.006861791480332613</v>
       </c>
       <c r="G12" t="n">
-        <v>0.002304533030837774</v>
+        <v>0.009833516553044319</v>
       </c>
       <c r="H12" t="n">
-        <v>0.004099972080439329</v>
+        <v>0.008241757750511169</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0011614840477705</v>
+        <v>0.008554537780582905</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0007797430735081434</v>
+        <v>0.006336529739201069</v>
       </c>
       <c r="K12" t="n">
-        <v>0.02189173176884651</v>
+        <v>0.03692744672298431</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001978922635316849</v>
+        <v>0.0101922582834959</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01560214348137379</v>
+        <v>0.01771515049040318</v>
       </c>
       <c r="N12" t="n">
-        <v>0.006255005020648241</v>
+        <v>0.0121775921434164</v>
       </c>
       <c r="O12" t="n">
-        <v>0.001794697367586195</v>
+        <v>0.0003449057694524527</v>
       </c>
       <c r="P12" t="n">
-        <v>0.001185495057143271</v>
+        <v>0.002130133798345923</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.00322849047370255</v>
+        <v>0.002628015587106347</v>
       </c>
       <c r="R12" t="n">
-        <v>0.001944284420460463</v>
+        <v>0.01161080226302147</v>
       </c>
       <c r="S12" t="n">
-        <v>0.001649635145440698</v>
+        <v>0.00193215417675674</v>
       </c>
       <c r="T12" t="n">
-        <v>0.004376377444714308</v>
+        <v>0.003516614902764559</v>
       </c>
       <c r="U12" t="n">
-        <v>1.296593109145761e-05</v>
+        <v>0.000769477803260088</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0007236648816615343</v>
+        <v>0.002503125462681055</v>
       </c>
       <c r="W12" t="n">
-        <v>0.001223614206537604</v>
+        <v>9.179546032100916e-05</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0002399843506282195</v>
+        <v>0.00234528910368681</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.002316733356565237</v>
+        <v>0.004061487503349781</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.003333220491185784</v>
+        <v>0.0003575969894882292</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.003583193989470601</v>
+        <v>0.002604465000331402</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.0004844078794121742</v>
+        <v>0.0004721703007817268</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.00504347775131464</v>
+        <v>0.004815362393856049</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.0009770197793841362</v>
+        <v>0.002593554090708494</v>
       </c>
       <c r="AE12" t="n">
-        <v>6.979249883443117e-05</v>
+        <v>0.008336880244314671</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.001538332435302436</v>
+        <v>0.003401427529752254</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.002275535138323903</v>
+        <v>0.005596320144832134</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.002107339445501566</v>
+        <v>0.001845127437263727</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.0007809916278347373</v>
+        <v>0.01127067767083645</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.0008483229903504252</v>
+        <v>0.001384945120662451</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.001271125394850969</v>
+        <v>0.002631925977766514</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.002656278200447559</v>
+        <v>0.006474048364907503</v>
       </c>
       <c r="AM12" t="n">
-        <v>9.462748130317777e-05</v>
+        <v>0.00379868084564805</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.001967964228242636</v>
+        <v>0.0001259569689864293</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.003588306251913309</v>
+        <v>0.0004332414246164262</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.001651891972869635</v>
+        <v>0.004980169702321291</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.003026031889021397</v>
+        <v>0.002986895386129618</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.001042600139044225</v>
+        <v>0.00532581890001893</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.315245966310613e-06</v>
+        <v>0.002085008192807436</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.003962119575589895</v>
+        <v>0.00283021992072463</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.01820545271039009</v>
+        <v>0.03211218863725662</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.004280108027160168</v>
+        <v>0.002927067689597607</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.004767477046698332</v>
+        <v>0.001681424444541335</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.001690026256255805</v>
+        <v>0.01257795561105013</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.001607106067240238</v>
+        <v>0.007336042355746031</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.000835749669931829</v>
+        <v>0.001808147178962827</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.002652955474331975</v>
+        <v>0.001472496194764972</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.000784540839958936</v>
+        <v>0.001142696943134069</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.004346685484051704</v>
+        <v>0.001985636074095964</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.001409901073202491</v>
+        <v>0.005250534974038601</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.004118717741221189</v>
+        <v>0.005042251665145159</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.002521950285881758</v>
+        <v>0.004519863985478878</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.004878808278590441</v>
+        <v>0.0007456514285877347</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.002219323301687837</v>
+        <v>0.006709928624331951</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.0003115875297226012</v>
+        <v>0.005492205265909433</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.005276320036500692</v>
+        <v>0.00608396902680397</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.0009241763618774712</v>
+        <v>0.007803457789123058</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.003303064033389091</v>
+        <v>0.0009370802436023951</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.003601133590564132</v>
+        <v>0.006297762505710125</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.000812167301774025</v>
+        <v>0.003395322943106294</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.001400201348587871</v>
+        <v>0.001276274328120053</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.006390348076820374</v>
+        <v>0.007751591503620148</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.001624531578272581</v>
+        <v>3.141927300021052e-05</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.0008918547537177801</v>
+        <v>0.008975474163889885</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.002177475253120065</v>
+        <v>0.0014021135866642</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.003005301347002387</v>
+        <v>0.0003280295059084892</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.001769402646459639</v>
+        <v>0.0003538300516083837</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.008787378668785095</v>
+        <v>0.01780226454138756</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.0009435181273147464</v>
+        <v>0.00390003714710474</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.00227796658873558</v>
+        <v>0.005416445899754763</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.002287188544869423</v>
+        <v>0.0005929389735683799</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.001066923490725458</v>
+        <v>0.001213134964928031</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.002042550593614578</v>
+        <v>0.00527005922049284</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.0003235331387259066</v>
+        <v>0.001589488936588168</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.002256168751046062</v>
+        <v>0.000324516964610666</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.0001367096410831437</v>
+        <v>0.0006151085253804922</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.00415341230109334</v>
+        <v>0.00937504880130291</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.000757418223656714</v>
+        <v>0.003523825434967875</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.001342139556072652</v>
+        <v>0.00152884132694453</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.0008384785032831132</v>
+        <v>0.001826400519348681</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.001041678595356643</v>
+        <v>0.0003854287497233599</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.0007302277954295278</v>
+        <v>0.0005363774253055453</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.0004036806058138609</v>
+        <v>0.001778739970177412</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.0006595211452804506</v>
+        <v>0.001036160392686725</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.007866551168262959</v>
+        <v>0.009668410755693913</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.002631722018122673</v>
+        <v>0.01574802026152611</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.0005324726807884872</v>
+        <v>0.006645744666457176</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.007683404255658388</v>
+        <v>0.008749064989387989</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.006520234048366547</v>
+        <v>0.0007601643446832895</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.002453233581036329</v>
+        <v>0.004136946052312851</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.005337046459317207</v>
+        <v>0.003122077323496342</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.006777374073863029</v>
+        <v>0.0004774872213602066</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.0001625257427804172</v>
+        <v>0.0002251378609798849</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.0006719677476212382</v>
+        <v>0.00220413925126195</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.003747478593140841</v>
+        <v>0.008796005509793758</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.001650928636081517</v>
+        <v>0.002780995797365904</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.002883469220250845</v>
+        <v>0.003160496242344379</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.00101289851590991</v>
+        <v>0.0003163993824273348</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.0007101313094608486</v>
+        <v>0.0009578070603311062</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.001373455277644098</v>
+        <v>0.0008108147885650396</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.0008911755285225809</v>
+        <v>0.0009404824231751263</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.43313518492505e-05</v>
+        <v>0.002547406358644366</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.002848365344107151</v>
+        <v>0.004244223237037659</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.0002124615712091327</v>
+        <v>0.001642233808524907</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.002175802597776055</v>
+        <v>0.0003652652376331389</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.003859329503029585</v>
+        <v>0.005666684824973345</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.001017273752950132</v>
+        <v>0.01065747812390327</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.000132251821924001</v>
+        <v>0.01232967805117369</v>
       </c>
       <c r="DK12" t="n">
-        <v>9.033136302605271e-05</v>
+        <v>0.001600661082193255</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.001581138232722878</v>
+        <v>0.003687581978738308</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.0008922094712033868</v>
+        <v>0.0005543580045923591</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.0001144923735409975</v>
+        <v>0.00508349621668458</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.0008948990143835545</v>
+        <v>0.007326429709792137</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.002163309836760163</v>
+        <v>0.0001909505517687649</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.003058963920921087</v>
+        <v>0.007529118098318577</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.0026127805467695</v>
+        <v>0.002224096795544028</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.0003030444495379925</v>
+        <v>0.0007007102249190211</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.0002397216885583475</v>
+        <v>0.0005747432005591691</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.001693193567916751</v>
+        <v>0.004522249568253756</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.002220205496996641</v>
+        <v>0.0007533752359449863</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.001370731508359313</v>
+        <v>0.003081298898905516</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.002397410338744521</v>
+        <v>0.003820273326709867</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.003006635466590524</v>
+        <v>0.002729982137680054</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.00113787455484271</v>
+        <v>2.99219973385334e-05</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.0002005323767662048</v>
+        <v>0.003898854833096266</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.0006766590522602201</v>
+        <v>0.0004736619594041258</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.001775635057128966</v>
+        <v>0.002357505727559328</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.001838086755014956</v>
+        <v>0.01135235652327538</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.0003064034390263259</v>
+        <v>0.005601642187684774</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.0003260623198002577</v>
+        <v>4.506082041189075e-05</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.002853359561413527</v>
+        <v>0.003287992905825377</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.001727991853840649</v>
+        <v>0.0007470916025340557</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.002923561492934823</v>
+        <v>0.009294695220887661</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.004314104560762644</v>
+        <v>0.0002158963470719755</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.0006429659551940858</v>
+        <v>0.001783218118362129</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.0007120741065591574</v>
+        <v>3.728902811417356e-06</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.0003352649218868464</v>
+        <v>0.0003989003598690033</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.000991866341792047</v>
+        <v>0.003400234272703528</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.0001455578021705151</v>
+        <v>0.002552471589297056</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.004483310971409082</v>
+        <v>0.00219567702151835</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.001940592541359365</v>
+        <v>0.003792584873735905</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.001703193527646363</v>
+        <v>0.0004000483313575387</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.0004354188276920468</v>
+        <v>0.00113315018825233</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.001288429019041359</v>
+        <v>0.004433632828295231</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.003264273516833782</v>
+        <v>3.021055636054371e-05</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.003816842334344983</v>
+        <v>0.0009659356437623501</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.003081798320636153</v>
+        <v>0.001648278092034161</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.00043765630107373</v>
+        <v>0.001068843645043671</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.003891615197062492</v>
+        <v>0.01126475818455219</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.001036220928654075</v>
+        <v>0.002394148148596287</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.001959110843017697</v>
+        <v>0.003305122721940279</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.000440368487033993</v>
+        <v>0.0009535655844956636</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.0004508529091253877</v>
+        <v>0.0003840842109639198</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.001158581348136067</v>
+        <v>0.001164570450782776</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.0003384279843885452</v>
+        <v>0.001426210394129157</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.0004746599588543177</v>
+        <v>0.001999314874410629</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.0002963683800771832</v>
+        <v>0.001623428077436984</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.001575548434630036</v>
+        <v>0.006176704075187445</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.005161426961421967</v>
+        <v>0.0006331149488687515</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.002566083334386349</v>
+        <v>0.006054509431123734</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.001360972877591848</v>
+        <v>0.0008722285274416208</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.0008491107728332281</v>
+        <v>0.003298553405329585</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.001023632124997675</v>
+        <v>0.001520027755759656</v>
       </c>
       <c r="FN12" t="n">
-        <v>3.768735041376203e-05</v>
+        <v>0.0003083834890276194</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.0008881108369678259</v>
+        <v>0.00245251227170229</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.00264901015907526</v>
+        <v>0.004596369806677103</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.001097355154342949</v>
+        <v>0.005874183960258961</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.004944325890392065</v>
+        <v>0.002675325144082308</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.002175896428525448</v>
+        <v>0.000173116335645318</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.003253344213590026</v>
+        <v>0.01230031903833151</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.002657542005181313</v>
+        <v>0.005390177015215158</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.00125755462795496</v>
+        <v>3.688689321279526e-05</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.0004856179875787348</v>
+        <v>0.004532902501523495</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.001518592122010887</v>
+        <v>5.417619831860065e-05</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.004361808300018311</v>
+        <v>0.0008955072844401002</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.001484389184042811</v>
+        <v>0.003472336800768971</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.002144872676581144</v>
+        <v>0.003030025865882635</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.001455323421396315</v>
+        <v>0.001795383752323687</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.0007801305036991835</v>
+        <v>0.001137879560701549</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.003843984566628933</v>
+        <v>0.003903171280398965</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.009056613780558109</v>
+        <v>0.00466953357681632</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.001379546825774014</v>
+        <v>0.005676089320331812</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.002989866537973285</v>
+        <v>0.001470284070819616</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.008470552042126656</v>
+        <v>0.0005411801976151764</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2703885734081268</v>
+        <v>0.00329734617844224</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1138880401849747</v>
+        <v>0.001103791641071439</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02686166949570179</v>
+        <v>0.001114423619583249</v>
       </c>
       <c r="E13" t="n">
-        <v>0.06162579730153084</v>
+        <v>5.327101098373532e-05</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03449483588337898</v>
+        <v>0.001320456387475133</v>
       </c>
       <c r="G13" t="n">
-        <v>0.02684349566698074</v>
+        <v>5.779805360361934e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>0.006958406418561935</v>
+        <v>3.319329698570073e-05</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0166374184191227</v>
+        <v>0.00202141422778368</v>
       </c>
       <c r="J13" t="n">
-        <v>0.04037036374211311</v>
+        <v>0.000478774105431512</v>
       </c>
       <c r="K13" t="n">
-        <v>0.219831794500351</v>
+        <v>0.003956052474677563</v>
       </c>
       <c r="L13" t="n">
-        <v>0.07793748378753662</v>
+        <v>0.001213661627843976</v>
       </c>
       <c r="M13" t="n">
-        <v>0.04635576158761978</v>
+        <v>0.001848586020059884</v>
       </c>
       <c r="N13" t="n">
-        <v>0.04302459955215454</v>
+        <v>0.0008522943244315684</v>
       </c>
       <c r="O13" t="n">
-        <v>0.02403596043586731</v>
+        <v>0.001627991441637278</v>
       </c>
       <c r="P13" t="n">
-        <v>0.01486489363014698</v>
+        <v>0.0002210634993389249</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0454489067196846</v>
+        <v>0.000829509284812957</v>
       </c>
       <c r="R13" t="n">
-        <v>0.02275429852306843</v>
+        <v>0.001477954559959471</v>
       </c>
       <c r="S13" t="n">
-        <v>0.006174187175929546</v>
+        <v>0.0002137176197720692</v>
       </c>
       <c r="T13" t="n">
-        <v>0.02243567258119583</v>
+        <v>0.0002564651367720217</v>
       </c>
       <c r="U13" t="n">
-        <v>0.01037906855344772</v>
+        <v>0.0004477453185245395</v>
       </c>
       <c r="V13" t="n">
-        <v>0.009536942467093468</v>
+        <v>0.0001977374486159533</v>
       </c>
       <c r="W13" t="n">
-        <v>0.001562380231916904</v>
+        <v>0.0001690960634732619</v>
       </c>
       <c r="X13" t="n">
-        <v>0.02150831930339336</v>
+        <v>0.0002790338767226785</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.0005898196250200272</v>
+        <v>0.0001163807610282674</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.05728831887245178</v>
+        <v>0.0004546694399323314</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.01155564468353987</v>
+        <v>0.001118652638979256</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.003654682077467442</v>
+        <v>0.0009839989943429828</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.04582299292087555</v>
+        <v>0.0001124513000831939</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.01182537898421288</v>
+        <v>0.000314928765874356</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.0005629216320812702</v>
+        <v>0.001262611011043191</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0194521751254797</v>
+        <v>0.0006627261755056679</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.001566577702760696</v>
+        <v>0.0004154399503022432</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.01965050026774406</v>
+        <v>0.0007996698259375989</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.02145804092288017</v>
+        <v>0.0006623509107157588</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.01619178615510464</v>
+        <v>0.00064641929930076</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.04029420763254166</v>
+        <v>0.0003427086630836129</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.01915897242724895</v>
+        <v>0.0007247222238220274</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.03371468931436539</v>
+        <v>1.340488961432129e-05</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.003912846557796001</v>
+        <v>1.086678821593523e-05</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.005491804797202349</v>
+        <v>0.0005776877515017986</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.03729970753192902</v>
+        <v>2.710250555537641e-06</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.004604061134159565</v>
+        <v>0.0004237511893734336</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.002529871882870793</v>
+        <v>1.081937807612121e-05</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.02214272320270538</v>
+        <v>3.865535836666822e-05</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.008388334885239601</v>
+        <v>0.0004402979393489659</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.1426878571510315</v>
+        <v>0.001996464096009731</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.04719049483537674</v>
+        <v>0.0004542226670309901</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.01429998129606247</v>
+        <v>0.0006370429182425141</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.02934888750314713</v>
+        <v>0.001145804300904274</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.03010068833827972</v>
+        <v>0.0007288899505510926</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.03113382682204247</v>
+        <v>2.612573734950274e-05</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.003468126291409135</v>
+        <v>0.0007447990938089788</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.03165318816900253</v>
+        <v>0.0007660225383006036</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.003633022308349609</v>
+        <v>0.0003268892760388553</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.08171185851097107</v>
+        <v>2.199044683948159e-05</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.05934037640690804</v>
+        <v>0.001059671863913536</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.01028682477772236</v>
+        <v>0.0006338272360153496</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.01920597068965435</v>
+        <v>0.0002820415247697383</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.02841269783675671</v>
+        <v>0.0004990471643395722</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.004741019569337368</v>
+        <v>5.298104952089489e-06</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.04038112610578537</v>
+        <v>0.001198794459924102</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.01817730627954006</v>
+        <v>0.0008269320242106915</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.01145474798977375</v>
+        <v>0.0001281784061575308</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.05375731363892555</v>
+        <v>0.0002312172728125006</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.03083842620253563</v>
+        <v>6.356494850479066e-05</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.007127861492335796</v>
+        <v>0.0006587300449609756</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.004074492491781712</v>
+        <v>0.0001598238886799663</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.02435809373855591</v>
+        <v>0.0001100641311495565</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.02065270580351353</v>
+        <v>0.000147617349284701</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.000438361894339323</v>
+        <v>8.767715189605951e-05</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.02419999055564404</v>
+        <v>0.0001212563220178708</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.006239723414182663</v>
+        <v>0.0001752702373778448</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.06856898218393326</v>
+        <v>0.001660701935179532</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.0655546709895134</v>
+        <v>0.0001931650476763025</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.01524824649095535</v>
+        <v>9.02808242244646e-05</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.02743257768452168</v>
+        <v>0.0002439211239106953</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.01505301333963871</v>
+        <v>0.0007213125936686993</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.008079580031335354</v>
+        <v>0.0002543716400396079</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.002607285510748625</v>
+        <v>0.0003104660427197814</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.005113512743264437</v>
+        <v>0.00110322015825659</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.007299689576029778</v>
+        <v>9.818388207349926e-05</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.04740438237786293</v>
+        <v>0.001001360360532999</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.006305425427854061</v>
+        <v>0.0002568508207332343</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.005579016171395779</v>
+        <v>0.0008048743475228548</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.02200199104845524</v>
+        <v>7.099946378730237e-05</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.004611825570464134</v>
+        <v>0.0003539007448125631</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.01186761632561684</v>
+        <v>0.0002020831452682614</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.01231157220900059</v>
+        <v>8.489044557791203e-05</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.005920770112425089</v>
+        <v>0.0003417022817302495</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.04296036809682846</v>
+        <v>0.0001317983696935698</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.02093463763594627</v>
+        <v>0.001108446856960654</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.01358634140342474</v>
+        <v>8.785481622908264e-05</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.01643460988998413</v>
+        <v>0.002221955452114344</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.01171394065022469</v>
+        <v>0.001037325244396925</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0602000430226326</v>
+        <v>0.001066816505044699</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.0439043827354908</v>
+        <v>5.698857421521097e-05</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.01577568612992764</v>
+        <v>0.0002349531860090792</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.02827655151486397</v>
+        <v>0.0003321415861137211</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.006910395808517933</v>
+        <v>2.390716326772235e-05</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.04620373621582985</v>
+        <v>0.0009996804874390364</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.01199546176940203</v>
+        <v>0.0002084800653392449</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.01426183246076107</v>
+        <v>0.0008396446937695146</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.02974817529320717</v>
+        <v>6.678185309283435e-05</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.006303736008703709</v>
+        <v>0.0005094229127280414</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0124198142439127</v>
+        <v>0.0002354402968194336</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.01627026870846748</v>
+        <v>0.0002848638978321105</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.001562827033922076</v>
+        <v>0.0006072008400224149</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.04725876450538635</v>
+        <v>3.406383621040732e-05</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.05286617204546928</v>
+        <v>0.0004793980624526739</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.004033959470689297</v>
+        <v>0.0004867514362558722</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.0543866753578186</v>
+        <v>0.0001610336184967309</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.0405244268476963</v>
+        <v>0.001892807427793741</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.03829517215490341</v>
+        <v>0.001107339863665402</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.002220053225755692</v>
+        <v>0.0003091906837653369</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.02183861844241619</v>
+        <v>0.001628575613722205</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.03982254862785339</v>
+        <v>0.0007939883507788181</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.009611411020159721</v>
+        <v>0.0001526653650216758</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.02301420085132122</v>
+        <v>0.000177238107426092</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.009580580517649651</v>
+        <v>9.329240128863603e-05</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.0200444795191288</v>
+        <v>0.0004039315390400589</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.005784009117633104</v>
+        <v>0.0003725215792655945</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.01199579332023859</v>
+        <v>0.0001085237017832696</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.01340471394360065</v>
+        <v>0.0007771655800752342</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.02880650758743286</v>
+        <v>0.0006329413154162467</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.01998312026262283</v>
+        <v>0.0004395970026962459</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.004437556490302086</v>
+        <v>0.0003178687184117734</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.04455491155385971</v>
+        <v>0.0002962378493975848</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.0210171602666378</v>
+        <v>0.0001358271110802889</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.001337788067758083</v>
+        <v>0.0006204155506566167</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.007796206511557102</v>
+        <v>0.0001416715094819665</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.0217187013477087</v>
+        <v>0.001104097347706556</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.007556492928415537</v>
+        <v>0.0006032528472132981</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.001133659388870001</v>
+        <v>0.0008864652481861413</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.01528788171708584</v>
+        <v>0.001251832349225879</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.02842530980706215</v>
+        <v>0.0002686892403289676</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.02787721529603004</v>
+        <v>0.0007812894182279706</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.01712825894355774</v>
+        <v>4.718007403425872e-06</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.006195398047566414</v>
+        <v>0.0006205789977684617</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.002327853813767433</v>
+        <v>4.89842495881021e-05</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.009812943637371063</v>
+        <v>0.0002175553381675854</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.006100752390921116</v>
+        <v>0.0001347192737739533</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.0001756497658789158</v>
+        <v>2.962122380267829e-06</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.003945449367165565</v>
+        <v>0.0002039460523519665</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.0001301146112382412</v>
+        <v>0.0004182311822660267</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.03568445891141891</v>
+        <v>0.0009915408445522189</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.01225990056991577</v>
+        <v>2.117162694048602e-05</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.01704124920070171</v>
+        <v>0.0004000315093435347</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.04034117609262466</v>
+        <v>0.0003644197131507099</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.01688701286911964</v>
+        <v>2.608166687423363e-05</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.02981240674853325</v>
+        <v>0.0001202312269015238</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.03895566985011101</v>
+        <v>0.0001909692364279181</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.05012222006917</v>
+        <v>0.0001713686069706455</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.01342685520648956</v>
+        <v>3.528250817907974e-05</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.04536071047186852</v>
+        <v>0.00119753263425082</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.009124330244958401</v>
+        <v>0.0002140645665349439</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.006368489935994148</v>
+        <v>0.0008842034148983657</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.02704738639295101</v>
+        <v>2.131107612513006e-05</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.01009768713265657</v>
+        <v>0.0004820549511350691</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.01849189400672913</v>
+        <v>0.0001571891771163791</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.01623418368399143</v>
+        <v>0.0002946722670458257</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.01032263599336147</v>
+        <v>0.0005626571364700794</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.007750993594527245</v>
+        <v>0.0001071937003871426</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.01222531963139772</v>
+        <v>0.0004921084037050605</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.01782859861850739</v>
+        <v>0.0005610919906757772</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.01616217195987701</v>
+        <v>0.0003452630480751395</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.04057909548282623</v>
+        <v>0.0004556501808110625</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.007841167040169239</v>
+        <v>0.0001112945028580725</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.004511931445449591</v>
+        <v>0.0006150273256935179</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.02605859935283661</v>
+        <v>0.001062787720002234</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.02996622584760189</v>
+        <v>0.0004162645782344043</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.03092149458825588</v>
+        <v>0.0004163657722529024</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.008059829473495483</v>
+        <v>0.001012789434753358</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.05255837738513947</v>
+        <v>0.0003167265676893294</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.008367480710148811</v>
+        <v>0.001046515535563231</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.01022344548255205</v>
+        <v>0.00101430295035243</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.02051020599901676</v>
+        <v>7.618451490998268e-06</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.01293567568063736</v>
+        <v>0.0001970562880160287</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.005414047744125128</v>
+        <v>0.0002488247118890285</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.01500506699085236</v>
+        <v>7.695233216509223e-05</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.02673418633639812</v>
+        <v>0.0001508491550339386</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.0244535319507122</v>
+        <v>0.0007968402933329344</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.03276589512825012</v>
+        <v>0.0002724325167946517</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.0006672530435025692</v>
+        <v>0.0004141920071560889</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.002679275348782539</v>
+        <v>0.0008374305907636881</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.01628188788890839</v>
+        <v>0.001321773510426283</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.0395660474896431</v>
+        <v>0.0005689286626875401</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.09976261854171753</v>
+        <v>0.0004840202745981514</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.02178124152123928</v>
+        <v>0.0005595447728410363</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.000907350389752537</v>
+        <v>0.003290480002760887</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01268154568970203</v>
+        <v>0.141123428940773</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0007322457386180758</v>
+        <v>0.0004507628036662936</v>
       </c>
       <c r="D14" t="n">
-        <v>0.003431201912462711</v>
+        <v>0.05776182562112808</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001510578207671642</v>
+        <v>0.03680676966905594</v>
       </c>
       <c r="F14" t="n">
-        <v>0.008244827389717102</v>
+        <v>0.1518245041370392</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001664055860601366</v>
+        <v>0.03631100058555603</v>
       </c>
       <c r="H14" t="n">
-        <v>0.004313571378588676</v>
+        <v>0.09693513810634613</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0003180251223966479</v>
+        <v>0.01716886833310127</v>
       </c>
       <c r="J14" t="n">
-        <v>0.002207092009484768</v>
+        <v>0.01009798422455788</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01174016669392586</v>
+        <v>0.1979241073131561</v>
       </c>
       <c r="L14" t="n">
-        <v>0.000193328145542182</v>
+        <v>0.0318613313138485</v>
       </c>
       <c r="M14" t="n">
-        <v>0.002851213794201612</v>
+        <v>0.1257642060518265</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0007561584934592247</v>
+        <v>0.003971129655838013</v>
       </c>
       <c r="O14" t="n">
-        <v>0.006532726809382439</v>
+        <v>0.2017428874969482</v>
       </c>
       <c r="P14" t="n">
-        <v>0.002566480077803135</v>
+        <v>0.005843351129442453</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.002228441881015897</v>
+        <v>0.01624388620257378</v>
       </c>
       <c r="R14" t="n">
-        <v>8.402322418987751e-05</v>
+        <v>0.05453179031610489</v>
       </c>
       <c r="S14" t="n">
-        <v>9.838283585850149e-05</v>
+        <v>0.01406653039157391</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0009660638170316815</v>
+        <v>0.04252107441425323</v>
       </c>
       <c r="U14" t="n">
-        <v>0.000270371267106384</v>
+        <v>0.003216336481273174</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0007180067477747798</v>
+        <v>0.04622988402843475</v>
       </c>
       <c r="W14" t="n">
-        <v>0.00126212986651808</v>
+        <v>0.01351368986070156</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0009820389095693827</v>
+        <v>0.01462535187602043</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0001089951547328383</v>
+        <v>0.02242928743362427</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.001024381257593632</v>
+        <v>0.0359705463051796</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0007396464934572577</v>
+        <v>0.01302520744502544</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0002037471276707947</v>
+        <v>0.02820008993148804</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.0009387811296619475</v>
+        <v>0.0138298636302352</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0006007151678204536</v>
+        <v>0.002346776891499758</v>
       </c>
       <c r="AE14" t="n">
-        <v>8.703465573489666e-05</v>
+        <v>0.06535186618566513</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.00108433049172163</v>
+        <v>0.09902957081794739</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0004504704265855253</v>
+        <v>0.003975863102823496</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.176115908194333e-05</v>
+        <v>0.0002169366925954819</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0009275198681280017</v>
+        <v>0.1078341081738472</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.0008514010114595294</v>
+        <v>0.02232770994305611</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.001309084007516503</v>
+        <v>0.01062251906841993</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.00151150964666158</v>
+        <v>0.03275604918599129</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.0005663918564096093</v>
+        <v>4.422897472977638e-05</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.0006480367155745625</v>
+        <v>0.015227185562253</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.001207529101520777</v>
+        <v>0.02446682006120682</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.002601188607513905</v>
+        <v>0.02515705861151218</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.000929299567360431</v>
+        <v>0.03007977269589901</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.0009196283062919974</v>
+        <v>0.06237144395709038</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.0008783219382166862</v>
+        <v>0.003749536816030741</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.0001428388059139252</v>
+        <v>0.01877466402947903</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.007330531720072031</v>
+        <v>0.2870701253414154</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.001992098987102509</v>
+        <v>0.01028412021696568</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.0009276012424379587</v>
+        <v>0.04406880959868431</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.001253872876986861</v>
+        <v>0.02720854245126247</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.004980628378689289</v>
+        <v>0.1386539489030838</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.001629196107387543</v>
+        <v>0.003306131809949875</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.001922569470480084</v>
+        <v>0.01710437797009945</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.001222708146087825</v>
+        <v>0.01041416265070438</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.0005587116465903819</v>
+        <v>0.005911595188081264</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.001967387739568949</v>
+        <v>0.08083761483430862</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.002332083415240049</v>
+        <v>0.005099969450384378</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.001848530955612659</v>
+        <v>0.0398838222026825</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.003351767314597964</v>
+        <v>0.03709247708320618</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.002783280331641436</v>
+        <v>0.02286626771092415</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.0001026800455292687</v>
+        <v>0.01594594866037369</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.0003924043849110603</v>
+        <v>0.0624476931989193</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.0008569399360567331</v>
+        <v>0.003050995990633965</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.0004480156640056521</v>
+        <v>0.02351075783371925</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.001082832110114396</v>
+        <v>0.0546576976776123</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.0002430957974866033</v>
+        <v>0.0305359736084938</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.0001236133684869856</v>
+        <v>0.005926739424467087</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.000309035851387307</v>
+        <v>0.01836122199892998</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.0005600318545475602</v>
+        <v>0.0002216729335486889</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.001287967665120959</v>
+        <v>0.07340464740991592</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.0005797009216621518</v>
+        <v>0.01646754518151283</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.0002618745202198625</v>
+        <v>0.03115494176745415</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.0001126764691434801</v>
+        <v>0.001266916748136282</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.004339274019002914</v>
+        <v>0.1267572045326233</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.0007182520930655301</v>
+        <v>0.01019955612719059</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.000535517290700227</v>
+        <v>0.02722820639610291</v>
       </c>
       <c r="BY14" t="n">
-        <v>9.422916627954692e-05</v>
+        <v>0.01996007934212685</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.002382739912718534</v>
+        <v>0.07299993187189102</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.0002045993751380593</v>
+        <v>0.04505838826298714</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.0006742522236891091</v>
+        <v>0.01681458950042725</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.0007697620894759893</v>
+        <v>0.02033632434904575</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.000311045499984175</v>
+        <v>0.01376457046717405</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.002237652195617557</v>
+        <v>0.05340762063860893</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.0002989050117321312</v>
+        <v>0.0146580096334219</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.0004559916560538113</v>
+        <v>0.01578907854855061</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.0006630182033404708</v>
+        <v>0.002024848014116287</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.0005411102902144194</v>
+        <v>0.03310767188668251</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.0009993496350944042</v>
+        <v>0.01845451816916466</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.0006296471692621708</v>
+        <v>0.006838308181613684</v>
       </c>
       <c r="CL14" t="n">
-        <v>3.490792005322874e-05</v>
+        <v>0.0001858739415183663</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.001920577138662338</v>
+        <v>0.04598703235387802</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.000150833380757831</v>
+        <v>0.1001042127609253</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.0003768638707697392</v>
+        <v>0.04523920640349388</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.001928457757458091</v>
+        <v>0.08920552581548691</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.0006776266964152455</v>
+        <v>0.02929830364882946</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.001447192626073956</v>
+        <v>0.01536146365106106</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.001319065107963979</v>
+        <v>0.002507869154214859</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.0007694929372519255</v>
+        <v>0.001407189294695854</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.0001742204185575247</v>
+        <v>0.000246663810685277</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.0003174963349010795</v>
+        <v>0.0268065370619297</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.002193519845604897</v>
+        <v>0.04792720824480057</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.0002998813288286328</v>
+        <v>0.01942890137434006</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.0008555952226743102</v>
+        <v>0.02769107185304165</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.0009214989258907735</v>
+        <v>0.01111630536615849</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.0007143233087845147</v>
+        <v>0.04462094977498055</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.000866295478772372</v>
+        <v>0.004052006173878908</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.001243749749846756</v>
+        <v>0.001831361558288336</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.0001184482534881681</v>
+        <v>0.005535742733627558</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.001025611185468733</v>
+        <v>0.02041600272059441</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.003121317131444812</v>
+        <v>0.01737723127007484</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.0008600055589340627</v>
+        <v>0.02286718785762787</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.003108303062617779</v>
+        <v>0.006575598381459713</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.00463974243029952</v>
+        <v>0.05570270121097565</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.003132854355499148</v>
+        <v>0.01804842799901962</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.0008251445251516998</v>
+        <v>0.04288448393344879</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.002843593945726752</v>
+        <v>0.01413963176310062</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.001470705610699952</v>
+        <v>0.05649661272764206</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.0003131342527922243</v>
+        <v>0.01635205559432507</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.0005775841418653727</v>
+        <v>0.004006263799965382</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.0004121709789615124</v>
+        <v>0.01715283654630184</v>
       </c>
       <c r="DQ14" t="n">
-        <v>4.069741407874972e-05</v>
+        <v>0.04152931645512581</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.0001669169869273901</v>
+        <v>0.0151709234341979</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.001368573284707963</v>
+        <v>0.04056927189230919</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.0002416052739135921</v>
+        <v>0.02071043476462364</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.0001808419183362275</v>
+        <v>0.01008588075637817</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.0006266350974328816</v>
+        <v>0.03255387768149376</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.0001593966298969463</v>
+        <v>0.01619850471615791</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.001133845071308315</v>
+        <v>0.03833095729351044</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.0007781083695590496</v>
+        <v>0.0164266973733902</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.0007085920660756528</v>
+        <v>0.00288054347038269</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.000451358500868082</v>
+        <v>0.01289799995720387</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.000835361541248858</v>
+        <v>0.00285894819535315</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.0006183597724884748</v>
+        <v>0.02509808540344238</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.0009318147785961628</v>
+        <v>0.03717773407697678</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.001098297885619104</v>
+        <v>0.0719938725233078</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.0009117292938753963</v>
+        <v>0.006952723022550344</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.002263124566525221</v>
+        <v>0.01607582159340382</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.0006651678122580051</v>
+        <v>0.01762570813298225</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.0004510232247412205</v>
+        <v>0.01165657304227352</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.0002524036390241235</v>
+        <v>0.01586952805519104</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.0002912102499976754</v>
+        <v>0.008963317610323429</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.0008906494476832449</v>
+        <v>0.0004759994335472584</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.0002389359724475071</v>
+        <v>0.01529063656926155</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.0002592047967482358</v>
+        <v>0.004827032331377268</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.000520318397320807</v>
+        <v>0.03155503794550896</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.002287334762513638</v>
+        <v>0.04577915370464325</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.0006171435234136879</v>
+        <v>0.01904527470469475</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.0009412061772309244</v>
+        <v>0.04012763872742653</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.001289759064093232</v>
+        <v>0.00773351825773716</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.0008482705452479422</v>
+        <v>0.007501367479562759</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.001037852140143514</v>
+        <v>0.01468182727694511</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.00160509895067662</v>
+        <v>0.03010673820972443</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.0007555900956504047</v>
+        <v>0.007439335808157921</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.0005188659415580332</v>
+        <v>0.01850370317697525</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.002239650348201394</v>
+        <v>0.06222371384501457</v>
       </c>
       <c r="EZ14" t="n">
-        <v>1.743232132866979e-05</v>
+        <v>0.00682914350181818</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.000245267990976572</v>
+        <v>0.02623666636645794</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.0008051072363741696</v>
+        <v>0.01623527333140373</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.0005312031134963036</v>
+        <v>0.03565440326929092</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.001179489307105541</v>
+        <v>0.01997596584260464</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.001243575708940625</v>
+        <v>0.002323519205674529</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.00036618672311306</v>
+        <v>0.007923447526991367</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.0006627911934629083</v>
+        <v>0.008762424811720848</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.0004267643671482801</v>
+        <v>0.01930616423487663</v>
       </c>
       <c r="FI14" t="n">
-        <v>2.124934690073133e-05</v>
+        <v>0.0008280258625745773</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.001413983525708318</v>
+        <v>0.03771987929940224</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.0006030464428476989</v>
+        <v>0.02863926626741886</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.001382382237352431</v>
+        <v>0.06404396891593933</v>
       </c>
       <c r="FM14" t="n">
-        <v>7.104018004611135e-05</v>
+        <v>0.02351828664541245</v>
       </c>
       <c r="FN14" t="n">
-        <v>1.648563193157315e-05</v>
+        <v>0.01962187141180038</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.0008101864950731397</v>
+        <v>0.07526402175426483</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.001444882829673588</v>
+        <v>0.01162587758153677</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.0002008371957344934</v>
+        <v>0.01441880594938993</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.001556604402139783</v>
+        <v>0.05171893909573555</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.0002729178522713482</v>
+        <v>0.01811109110713005</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.001760825631208718</v>
+        <v>0.06715662032365799</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.0006803293363191187</v>
+        <v>0.02138594910502434</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.0002741203061304986</v>
+        <v>0.005705768242478371</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.0001327659556409344</v>
+        <v>0.1035436913371086</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.001009470550343394</v>
+        <v>0.02959230728447437</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.001833660062402487</v>
+        <v>0.001948252320289612</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.0007023223442956805</v>
+        <v>0.00618731090798974</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.0009577304008416831</v>
+        <v>0.0327528715133667</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.0004784695629496127</v>
+        <v>0.011818234808743</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.001821496756747365</v>
+        <v>0.05636446923017502</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.001523438608273864</v>
+        <v>0.01450648717582226</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.00153305206913501</v>
+        <v>0.05157880485057831</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.0001507874694652855</v>
+        <v>0.02189764566719532</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.0001318330760113895</v>
+        <v>0.002694775350391865</v>
       </c>
     </row>
     <row r="15">
